--- a/Working file.xlsx
+++ b/Working file.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swathirao/Documents/Notes/Data 201/Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8EE85BB-4860-2749-ADDD-FCE2B7F512C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C17A588-A13C-8249-B3C0-BA5D507D439A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="1" xr2:uid="{FA827ABB-7F19-A44A-951E-8E5375625068}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19620" activeTab="1" xr2:uid="{FA827ABB-7F19-A44A-951E-8E5375625068}"/>
   </bookViews>
   <sheets>
     <sheet name="Tables" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="179">
   <si>
     <t>Airline</t>
   </si>
@@ -87,9 +87,6 @@
     <t>Origin City Market ID</t>
   </si>
   <si>
-    <t>Can say a derived attribute. Its primary purpose is to group multiple airports that serve the exact same metropolitan area.In database design, it is stored explicitly in the final BTS tables (materialized) rather than calculated at runtime purely to optimize performance for analytical queries, saving data scientists from having to perform massive table joins every time they want to group multi-airport metros.</t>
-  </si>
-  <si>
     <t>Origin</t>
   </si>
   <si>
@@ -121,9 +118,6 @@
   </si>
   <si>
     <t>Yes; get carrier name, remove last 5 chars</t>
-  </si>
-  <si>
-    <t>world are code, check if it is really needed; not of use now, check if state maps exaclt yot 1 wac to keep it with state</t>
   </si>
   <si>
     <t>Destination</t>
@@ -379,9 +373,6 @@
     <t>DivAirportID</t>
   </si>
   <si>
-    <t>Is sufficient for finding opeartional bottleneck</t>
-  </si>
-  <si>
     <t>used for identifying legal violations and extreme operational failures</t>
   </si>
   <si>
@@ -526,9 +517,6 @@
     <t>DivDist depends on(DestAirportID,DivAirportID)</t>
   </si>
   <si>
-    <t>Clean 3NF or we can retain this in Flights table and explain the choice- would avoid unnecessary joins if need to calculate average speed</t>
-  </si>
-  <si>
     <t>Derived attribute of DepDelay</t>
   </si>
   <si>
@@ -559,9 +547,6 @@
     <t>Columns selected</t>
   </si>
   <si>
-    <t>Suggestion : Lets keep the datsset wide and for finals, if certain columns are not required, we can simply DROP it. At later point, including columns might be cumbersome, might have to drop table and recreate to ensure accuracy.</t>
-  </si>
-  <si>
     <t>Calendar</t>
   </si>
   <si>
@@ -569,6 +554,30 @@
   </si>
   <si>
     <t>Can be derived from CRSElapsedTime + DivArrDelay - DepDelay</t>
+  </si>
+  <si>
+    <t>Is sufficient for finding operational bottleneck</t>
+  </si>
+  <si>
+    <t>Violation of 2NF, put itno separate table - Clean 3NF or we can retain this in Flights table and explain the choice- would avoid unnecessary joins if need to calculate average speed</t>
+  </si>
+  <si>
+    <t>The initial timestamp when the plane first pushed back from the gate (before turning around).For the vast majority of standard flights that do not experience a gate return, FirstDepTime will be completely blank (NaN or null).</t>
+  </si>
+  <si>
+    <t>world area code, not of use</t>
+  </si>
+  <si>
+    <t>Its primary purpose is to group multiple airports that serve the exact same metropolitan area.In database design, it is stored explicitly in the final BTS tables (materialized) rather than calculated at runtime purely to optimize performance for analytical queries, saving data scientists from having to perform massive table joins every time they want to group multi-airport metros.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suggestion : Lets keep the dataset wide until finals, if certain columns are not required, we can simply DROP it. At later point, including columns might be cumbersome, might have to drop table and recreate to ensure accuracy. </t>
+  </si>
+  <si>
+    <t>Marked in red font can be dropped; we can discuss if needed</t>
+  </si>
+  <si>
+    <t>Didn’t include quarter here as we are working with only 2 quarters data</t>
   </si>
 </sst>
 </file>
@@ -691,10 +700,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1043,7 +1052,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1" t="s">
@@ -1056,7 +1065,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1089,7 +1098,7 @@
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E5" s="6"/>
     </row>
@@ -1100,7 +1109,7 @@
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="D6" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E6" s="6"/>
     </row>
@@ -1120,7 +1129,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -1132,7 +1141,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="1"/>
@@ -1156,28 +1165,28 @@
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>15</v>
+        <v>175</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E13" s="6"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -1186,29 +1195,29 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E15" s="6"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E16" s="6"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -1216,13 +1225,13 @@
       <c r="E17" s="6"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
-        <v>22</v>
+      <c r="A18" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1" t="s">
-        <v>27</v>
+        <v>174</v>
       </c>
       <c r="E18" s="6"/>
     </row>
@@ -1235,7 +1244,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -1244,7 +1253,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -1260,7 +1269,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1269,7 +1278,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1278,77 +1287,77 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E25" s="6"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E26" s="6"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B27" s="1"/>
-      <c r="C27" s="14" t="s">
-        <v>60</v>
+      <c r="C27" s="15" t="s">
+        <v>58</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E27" s="6"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B28" s="1"/>
-      <c r="C28" s="14"/>
+      <c r="C28" s="15"/>
       <c r="D28" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E28" s="6"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E29" s="6"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E30" s="6"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -1357,23 +1366,23 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E32" s="6"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E33" s="6"/>
     </row>
@@ -1386,7 +1395,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -1395,7 +1404,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -1404,7 +1413,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -1413,7 +1422,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -1422,7 +1431,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -1431,33 +1440,33 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B40" s="1"/>
-      <c r="C40" s="14" t="s">
-        <v>60</v>
+      <c r="C40" s="15" t="s">
+        <v>58</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E40" s="6"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B41" s="1"/>
-      <c r="C41" s="14"/>
+      <c r="C41" s="15"/>
       <c r="D41" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -1466,7 +1475,7 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -1475,7 +1484,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -1491,7 +1500,7 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -1500,21 +1509,21 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
       <c r="D47" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E47" s="6"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
@@ -1522,12 +1531,12 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
       <c r="D49" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E49" s="6"/>
     </row>
@@ -1540,7 +1549,7 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -1549,56 +1558,56 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E52" s="6"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E53" s="6"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
       <c r="D54" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E54" s="6"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
       <c r="D55" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E55" s="6"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E56" s="6"/>
     </row>
@@ -1611,7 +1620,7 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -1620,58 +1629,58 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E59" s="9" t="s">
         <v>104</v>
-      </c>
-      <c r="E59" s="9" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E60" s="6"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E61" s="6"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A62" s="1" t="s">
-        <v>82</v>
+      <c r="A62" s="5" t="s">
+        <v>80</v>
       </c>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
       <c r="D62" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E62" s="6"/>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E63" s="6"/>
     </row>
@@ -1683,8 +1692,8 @@
       <c r="E64" s="6"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A65" s="15" t="s">
-        <v>99</v>
+      <c r="A65" s="14" t="s">
+        <v>97</v>
       </c>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -1693,35 +1702,36 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
-      <c r="D66" s="1"/>
-      <c r="E66" s="6"/>
+      <c r="D66" s="1" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
       <c r="D67" s="1" t="s">
-        <v>112</v>
+        <v>171</v>
       </c>
       <c r="E67" s="6"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A68" s="1" t="s">
-        <v>110</v>
+      <c r="A68" s="5" t="s">
+        <v>108</v>
       </c>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
       <c r="D68" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E68" s="6" t="s">
         <v>113</v>
-      </c>
-      <c r="E68" s="6" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
@@ -1732,8 +1742,8 @@
       <c r="E69" s="6"/>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A70" s="15" t="s">
-        <v>85</v>
+      <c r="A70" s="14" t="s">
+        <v>83</v>
       </c>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -1742,63 +1752,65 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C71" s="1"/>
       <c r="D71" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E71" s="6"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
       <c r="D72" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E72" s="6"/>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
       <c r="D73" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E73" s="6"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
       <c r="D74" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E74" s="6"/>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
       <c r="D75" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E75" s="6"/>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A76" s="3"/>
+      <c r="A76" s="3" t="s">
+        <v>169</v>
+      </c>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
       <c r="D76" s="1"/>
@@ -1813,7 +1825,7 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -1821,7 +1833,9 @@
       <c r="E78" s="6"/>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A79" s="6"/>
+      <c r="A79" s="6" t="s">
+        <v>177</v>
+      </c>
       <c r="B79" s="6"/>
       <c r="C79" s="6"/>
       <c r="D79" s="6"/>
@@ -1843,7 +1857,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1851,7 +1865,7 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="13" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -1859,7 +1873,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1867,7 +1881,7 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>9</v>
@@ -1878,7 +1892,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -1889,7 +1903,7 @@
         <v>1</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
@@ -1897,7 +1911,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1905,10 +1919,10 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -1916,7 +1930,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -1933,7 +1947,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -1986,10 +2000,10 @@
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="7" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
@@ -2004,17 +2018,17 @@
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -2022,7 +2036,7 @@
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -2030,7 +2044,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -2038,7 +2052,7 @@
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -2046,7 +2060,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -2054,17 +2068,17 @@
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -2077,7 +2091,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -2085,14 +2099,14 @@
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H15" s="1"/>
       <c r="J15" s="1"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -2100,16 +2114,16 @@
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="7" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="J16" s="1"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -2124,7 +2138,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -2138,7 +2152,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -2146,14 +2160,14 @@
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H19" s="1"/>
       <c r="J19" s="1"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -2161,17 +2175,17 @@
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -2179,17 +2193,17 @@
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -2197,14 +2211,14 @@
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -2212,7 +2226,7 @@
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
@@ -2220,7 +2234,7 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -2228,7 +2242,7 @@
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
@@ -2237,7 +2251,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -2245,7 +2259,7 @@
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
@@ -2254,7 +2268,7 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -2262,10 +2276,10 @@
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="11" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
@@ -2273,7 +2287,7 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -2281,10 +2295,10 @@
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="11" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
@@ -2292,7 +2306,7 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -2300,7 +2314,7 @@
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -2309,7 +2323,7 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -2317,7 +2331,7 @@
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -2326,7 +2340,7 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -2334,7 +2348,7 @@
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
@@ -2343,7 +2357,7 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -2351,7 +2365,7 @@
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -2360,7 +2374,7 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -2368,7 +2382,7 @@
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -2377,7 +2391,7 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -2385,7 +2399,7 @@
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -2394,7 +2408,7 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -2402,7 +2416,7 @@
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -2411,7 +2425,7 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -2419,7 +2433,7 @@
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -2428,7 +2442,7 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -2436,10 +2450,10 @@
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
       <c r="G36" s="11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
@@ -2447,7 +2461,7 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -2455,10 +2469,10 @@
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
@@ -2466,7 +2480,7 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -2474,7 +2488,7 @@
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
       <c r="G38" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
@@ -2482,7 +2496,7 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -2490,10 +2504,10 @@
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
       <c r="G39" s="11" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H39" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
@@ -2501,7 +2515,7 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -2509,10 +2523,10 @@
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
       <c r="G40" s="12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
@@ -2520,7 +2534,7 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -2528,7 +2542,7 @@
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
       <c r="G41" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
@@ -2536,7 +2550,7 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -2544,10 +2558,10 @@
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
       <c r="G42" s="12" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
@@ -2555,7 +2569,7 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -2563,7 +2577,7 @@
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
       <c r="G43" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
@@ -2572,7 +2586,7 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -2580,7 +2594,7 @@
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
       <c r="G44" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
@@ -2589,7 +2603,7 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -2597,7 +2611,7 @@
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
       <c r="G45" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
@@ -2606,7 +2620,7 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -2614,7 +2628,7 @@
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
       <c r="G46" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
@@ -2623,7 +2637,7 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -2631,10 +2645,10 @@
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
       <c r="G47" s="11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
@@ -2642,7 +2656,7 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -2655,7 +2669,7 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -2669,7 +2683,7 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -2677,7 +2691,7 @@
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
       <c r="G50" s="4" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
@@ -2686,7 +2700,7 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -2694,10 +2708,10 @@
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
       <c r="G51" s="7" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
@@ -2705,7 +2719,7 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -2713,7 +2727,7 @@
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
       <c r="G52" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
@@ -2722,7 +2736,7 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -2730,7 +2744,7 @@
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
       <c r="G53" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
@@ -2739,7 +2753,7 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -2771,10 +2785,10 @@
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
       <c r="G56" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
@@ -2788,7 +2802,7 @@
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
       <c r="G57" s="7" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
@@ -2802,7 +2816,7 @@
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
       <c r="G58" s="7" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
@@ -2816,7 +2830,7 @@
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
@@ -2831,7 +2845,7 @@
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
       <c r="G60" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
@@ -2839,7 +2853,7 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61" s="7" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -2847,7 +2861,7 @@
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
       <c r="G61" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
@@ -2856,77 +2870,79 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H62" s="1"/>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="H65" s="1"/>
+        <v>168</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="G66" s="7" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="G68" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="G69" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="G70" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="G72" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H72" s="1"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="G73" s="7" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="G74" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.2">
@@ -2934,20 +2950,17 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="G76" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="H76" s="1" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="G77" s="7" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="G78" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.2">
@@ -2955,38 +2968,41 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="G80" s="4" t="s">
-        <v>153</v>
+        <v>150</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="81" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G81" s="7" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="82" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G82" s="7" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="H82" s="1"/>
     </row>
     <row r="83" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G83" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="85" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G85" s="4" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="86" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G86" s="7" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="87" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G87" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="101" spans="7:7" x14ac:dyDescent="0.2">

--- a/Working file.xlsx
+++ b/Working file.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swathirao/Documents/Notes/Data 201/Project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swathirao/Documents/GitHub/DBMS-Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C17A588-A13C-8249-B3C0-BA5D507D439A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{745DBE0B-6C8C-2340-8C71-8AFE342AE60F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19620" activeTab="1" xr2:uid="{FA827ABB-7F19-A44A-951E-8E5375625068}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="1" xr2:uid="{FA827ABB-7F19-A44A-951E-8E5375625068}"/>
   </bookViews>
   <sheets>
     <sheet name="Tables" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="244">
   <si>
     <t>Airline</t>
   </si>
@@ -578,13 +578,208 @@
   </si>
   <si>
     <t>Didn’t include quarter here as we are working with only 2 quarters data</t>
+  </si>
+  <si>
+    <t>Col1 (Swathi)</t>
+  </si>
+  <si>
+    <t>Col2 (Priyanka)</t>
+  </si>
+  <si>
+    <t>Dropped</t>
+  </si>
+  <si>
+    <t>Additionally added columns for PK/FK, non-key attributes</t>
+  </si>
+  <si>
+    <t>YEAR</t>
+  </si>
+  <si>
+    <t>Additionally included columns</t>
+  </si>
+  <si>
+    <t>QUARTER</t>
+  </si>
+  <si>
+    <t>MONTH </t>
+  </si>
+  <si>
+    <t>DAY_OF_MONTH </t>
+  </si>
+  <si>
+    <t>DAY_OF_WEEK</t>
+  </si>
+  <si>
+    <t>FL_DATE </t>
+  </si>
+  <si>
+    <t>OP_CARRIER_AIRLINE_ID</t>
+  </si>
+  <si>
+    <t>OP_UNIQUE_CARRIER</t>
+  </si>
+  <si>
+    <t>OP_CARRIER_FL_NUM </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAIL_NUM </t>
+  </si>
+  <si>
+    <t>IATACode</t>
+  </si>
+  <si>
+    <t>This is unique id - needed</t>
+  </si>
+  <si>
+    <t>ORIGIN_STATE_ABR </t>
+  </si>
+  <si>
+    <t>ORIGIN_WAC</t>
+  </si>
+  <si>
+    <t>DEST_STATE_ABR </t>
+  </si>
+  <si>
+    <t>DEST_WAC</t>
+  </si>
+  <si>
+    <t>ORIGIN_AIRPORT_ID / DEST_AIRPORT_ID</t>
+  </si>
+  <si>
+    <t>ORIGIN / DEST</t>
+  </si>
+  <si>
+    <t>ORIGIN_STATE_NM / DEST_STATE_NM</t>
+  </si>
+  <si>
+    <t>CRS_DEP_TIME </t>
+  </si>
+  <si>
+    <t>DEP_TIME</t>
+  </si>
+  <si>
+    <t>DEP_DELAY</t>
+  </si>
+  <si>
+    <t>DEP_DELAY_NEW</t>
+  </si>
+  <si>
+    <t>DEP_DEL15</t>
+  </si>
+  <si>
+    <t>TAXI_OUT</t>
+  </si>
+  <si>
+    <t>WHEELS_OFF</t>
+  </si>
+  <si>
+    <t>WHEELS_ON</t>
+  </si>
+  <si>
+    <t>TAXI_IN</t>
+  </si>
+  <si>
+    <t>CRS_ARR_TIME</t>
+  </si>
+  <si>
+    <t>ARR_TIME</t>
+  </si>
+  <si>
+    <t>ARR_DELAY</t>
+  </si>
+  <si>
+    <t>ARR_DELAY_NEW</t>
+  </si>
+  <si>
+    <t>ARR_DEL15</t>
+  </si>
+  <si>
+    <t>CANCELLED </t>
+  </si>
+  <si>
+    <t>CANCELLATION_CODE </t>
+  </si>
+  <si>
+    <t>DIVERTED</t>
+  </si>
+  <si>
+    <t>CRS_ELAPSED_TIME</t>
+  </si>
+  <si>
+    <t>ACTUAL_ELAPSED_TIME,</t>
+  </si>
+  <si>
+    <t>AIR_TIME</t>
+  </si>
+  <si>
+    <t>DISTANCE</t>
+  </si>
+  <si>
+    <t>Columns converted to rows now, so added DelayID as PK</t>
+  </si>
+  <si>
+    <t>In raw dataset but not added here</t>
+  </si>
+  <si>
+    <t>CARRIER_DELAY, WEATHER_DELAY, NAS_DELAY, SECURITY_DELAY, LATE_AIRCRAFT_DELAY</t>
+  </si>
+  <si>
+    <t>DivDistance </t>
+  </si>
+  <si>
+    <t>TABLE - Flights</t>
+  </si>
+  <si>
+    <t>TABLE - FlightDiversion</t>
+  </si>
+  <si>
+    <t>TABLE - FlightDelay</t>
+  </si>
+  <si>
+    <t>TABLE - CancellationReason</t>
+  </si>
+  <si>
+    <t>Total unique column count</t>
+  </si>
+  <si>
+    <t>ORIGIN_CITY_NAME / DEST_CITY_NAME</t>
+  </si>
+  <si>
+    <t>Airports (Origin/Dest combined)</t>
+  </si>
+  <si>
+    <t>FlightDiversion</t>
+  </si>
+  <si>
+    <t>Tables - Main tables</t>
+  </si>
+  <si>
+    <t>Supporting tables</t>
+  </si>
+  <si>
+    <t>AirlineNames</t>
+  </si>
+  <si>
+    <t>AirportNames</t>
+  </si>
+  <si>
+    <t>FINAL COLUMN NAMES</t>
+  </si>
+  <si>
+    <t>Calendar/TimePeriod</t>
+  </si>
+  <si>
+    <t>Total table count</t>
+  </si>
+  <si>
+    <t>In raw dataset but not added here because of repeating group</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -644,6 +839,32 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Helvetica"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -683,7 +904,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -703,6 +924,20 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1852,10 +2087,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CA334EF-316D-FA44-936F-23AB3782E682}">
-  <dimension ref="A1:K101"/>
+  <dimension ref="A1:S101"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="11" max="11" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.83203125" customWidth="1"/>
+    <col min="13" max="13" width="0.1640625" customWidth="1"/>
+    <col min="14" max="14" width="33" customWidth="1"/>
+    <col min="15" max="15" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
         <v>167</v>
       </c>
@@ -1870,8 +2114,20 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="O1" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="P1" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>114</v>
       </c>
@@ -1889,8 +2145,16 @@
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="O2" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="P2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>115</v>
       </c>
@@ -1908,8 +2172,16 @@
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="O3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="P3" s="20" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>116</v>
       </c>
@@ -1927,8 +2199,16 @@
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="O4" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="P4" s="19" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>117</v>
       </c>
@@ -1944,8 +2224,16 @@
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="O5" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="P5" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>118</v>
       </c>
@@ -1959,8 +2247,16 @@
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="O6" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="P6" s="19" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>2</v>
       </c>
@@ -1974,7 +2270,7 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>1</v>
       </c>
@@ -1989,8 +2285,14 @@
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O8" t="s">
+        <v>1</v>
+      </c>
+      <c r="P8" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>3</v>
       </c>
@@ -2007,8 +2309,14 @@
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="P9" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>5</v>
       </c>
@@ -2025,8 +2333,14 @@
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P10" s="19" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>119</v>
       </c>
@@ -2041,8 +2355,14 @@
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O11" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P11" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>15</v>
       </c>
@@ -2058,7 +2378,7 @@
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>17</v>
       </c>
@@ -2075,8 +2395,14 @@
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O13" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="P13" s="20" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>19</v>
       </c>
@@ -2088,8 +2414,14 @@
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="J14" s="1"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O14" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="P14" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>20</v>
       </c>
@@ -2103,8 +2435,14 @@
       </c>
       <c r="H15" s="1"/>
       <c r="J15" s="1"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O15" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="P15" s="19" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>120</v>
       </c>
@@ -2120,8 +2458,17 @@
         <v>143</v>
       </c>
       <c r="J16" s="1"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="N16" t="s">
+        <v>195</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="P16" s="21" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>121</v>
       </c>
@@ -2135,8 +2482,14 @@
       </c>
       <c r="H17" s="1"/>
       <c r="J17" s="1"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O17" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="P17" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>122</v>
       </c>
@@ -2150,7 +2503,7 @@
       </c>
       <c r="J18" s="1"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>123</v>
       </c>
@@ -2165,7 +2518,7 @@
       <c r="H19" s="1"/>
       <c r="J19" s="1"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>124</v>
       </c>
@@ -2182,8 +2535,14 @@
       </c>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O20" t="s">
+        <v>31</v>
+      </c>
+      <c r="P20" s="20" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>31</v>
       </c>
@@ -2200,8 +2559,14 @@
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O21" t="s">
+        <v>32</v>
+      </c>
+      <c r="P21" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>32</v>
       </c>
@@ -2215,8 +2580,14 @@
       </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O22" t="s">
+        <v>33</v>
+      </c>
+      <c r="P22" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>34</v>
       </c>
@@ -2231,8 +2602,16 @@
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="O23" t="s">
+        <v>34</v>
+      </c>
+      <c r="P23" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>35</v>
       </c>
@@ -2248,8 +2627,16 @@
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="O24" t="s">
+        <v>35</v>
+      </c>
+      <c r="P24" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>38</v>
       </c>
@@ -2265,8 +2652,16 @@
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="O25" t="s">
+        <v>38</v>
+      </c>
+      <c r="P25" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>39</v>
       </c>
@@ -2284,8 +2679,16 @@
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="O26" t="s">
+        <v>39</v>
+      </c>
+      <c r="P26" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>125</v>
       </c>
@@ -2303,8 +2706,16 @@
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="O27" t="s">
+        <v>125</v>
+      </c>
+      <c r="P27" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>48</v>
       </c>
@@ -2320,8 +2731,16 @@
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="O28" t="s">
+        <v>48</v>
+      </c>
+      <c r="P28" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>49</v>
       </c>
@@ -2337,8 +2756,16 @@
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="O29" t="s">
+        <v>49</v>
+      </c>
+      <c r="P29" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
         <v>50</v>
       </c>
@@ -2354,8 +2781,16 @@
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="O30" t="s">
+        <v>50</v>
+      </c>
+      <c r="P30" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>53</v>
       </c>
@@ -2371,8 +2806,16 @@
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="O31" t="s">
+        <v>51</v>
+      </c>
+      <c r="P31" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
         <v>54</v>
       </c>
@@ -2388,8 +2831,16 @@
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="O32" t="s">
+        <v>53</v>
+      </c>
+      <c r="P32" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>60</v>
       </c>
@@ -2405,8 +2856,16 @@
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="O33" t="s">
+        <v>54</v>
+      </c>
+      <c r="P33" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
         <v>61</v>
       </c>
@@ -2422,8 +2881,10 @@
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>62</v>
       </c>
@@ -2439,8 +2900,10 @@
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
         <v>77</v>
       </c>
@@ -2458,8 +2921,16 @@
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="O36" t="s">
+        <v>60</v>
+      </c>
+      <c r="P36" s="20" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
         <v>78</v>
       </c>
@@ -2477,8 +2948,16 @@
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="O37" t="s">
+        <v>61</v>
+      </c>
+      <c r="P37" s="19" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
         <v>79</v>
       </c>
@@ -2493,8 +2972,16 @@
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="O38" t="s">
+        <v>62</v>
+      </c>
+      <c r="P38" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
         <v>81</v>
       </c>
@@ -2512,8 +2999,10 @@
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
         <v>65</v>
       </c>
@@ -2531,8 +3020,16 @@
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="O40" t="s">
+        <v>77</v>
+      </c>
+      <c r="P40" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
         <v>67</v>
       </c>
@@ -2547,8 +3044,16 @@
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="O41" t="s">
+        <v>78</v>
+      </c>
+      <c r="P41" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
         <v>68</v>
       </c>
@@ -2566,8 +3071,16 @@
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+      <c r="O42" t="s">
+        <v>79</v>
+      </c>
+      <c r="P42" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
         <v>69</v>
       </c>
@@ -2583,8 +3096,16 @@
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="1"/>
+      <c r="M43" s="1"/>
+      <c r="O43" t="s">
+        <v>81</v>
+      </c>
+      <c r="P43" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
         <v>70</v>
       </c>
@@ -2600,8 +3121,10 @@
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+    </row>
+    <row r="45" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
         <v>106</v>
       </c>
@@ -2617,8 +3140,16 @@
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="18" t="s">
+        <v>224</v>
+      </c>
+      <c r="O45" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
         <v>107</v>
       </c>
@@ -2634,8 +3165,16 @@
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="1"/>
+      <c r="M46" s="1"/>
+      <c r="O46" t="s">
+        <v>148</v>
+      </c>
+      <c r="P46" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
         <v>84</v>
       </c>
@@ -2653,8 +3192,10 @@
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
         <v>86</v>
       </c>
@@ -2666,8 +3207,10 @@
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="1"/>
+      <c r="M48" s="1"/>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
         <v>88</v>
       </c>
@@ -2680,8 +3223,16 @@
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="1"/>
+      <c r="M49" s="1"/>
+      <c r="O49" t="s">
+        <v>84</v>
+      </c>
+      <c r="P49" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
         <v>90</v>
       </c>
@@ -2689,16 +3240,26 @@
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
-      <c r="G50" s="4" t="s">
+      <c r="F50" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="G50" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="H50" s="1"/>
+      <c r="H50" s="5"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="1"/>
+      <c r="M50" s="1"/>
+      <c r="O50" t="s">
+        <v>152</v>
+      </c>
+      <c r="P50" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
         <v>92</v>
       </c>
@@ -2707,17 +3268,25 @@
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
-      <c r="G51" s="7" t="s">
+      <c r="G51" s="17" t="s">
         <v>135</v>
       </c>
-      <c r="H51" s="1" t="s">
+      <c r="H51" s="5" t="s">
         <v>163</v>
       </c>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="1"/>
+      <c r="M51" s="1"/>
+      <c r="O51" t="s">
+        <v>88</v>
+      </c>
+      <c r="P51" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
         <v>111</v>
       </c>
@@ -2726,15 +3295,23 @@
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
-      <c r="G52" s="1" t="s">
+      <c r="G52" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="H52" s="1"/>
+      <c r="H52" s="5"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="1"/>
+      <c r="M52" s="1"/>
+      <c r="O52" t="s">
+        <v>90</v>
+      </c>
+      <c r="P52" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
         <v>112</v>
       </c>
@@ -2743,15 +3320,23 @@
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
-      <c r="G53" s="1" t="s">
+      <c r="G53" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="H53" s="1"/>
+      <c r="H53" s="5"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="1"/>
+      <c r="M53" s="1"/>
+      <c r="O53" t="s">
+        <v>92</v>
+      </c>
+      <c r="P53" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
         <v>126</v>
       </c>
@@ -2765,8 +3350,16 @@
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L54" s="1"/>
+      <c r="M54" s="1"/>
+      <c r="O54" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="P54" s="21" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
@@ -2777,8 +3370,17 @@
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="1"/>
+      <c r="M55" s="1"/>
+      <c r="O55" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="P55" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="S55" s="20"/>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
@@ -2793,8 +3395,16 @@
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="1"/>
+      <c r="M56" s="1"/>
+      <c r="O56" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="P56" s="21" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -2807,8 +3417,16 @@
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
       <c r="K57" s="1"/>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="1"/>
+      <c r="M57" s="1"/>
+      <c r="O57" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="P57" s="21" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -2821,8 +3439,12 @@
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
       <c r="K58" s="1"/>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="1"/>
+      <c r="M58" s="1"/>
+      <c r="O58" s="1"/>
+      <c r="P58" s="21"/>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -2836,8 +3458,10 @@
       <c r="I59" s="1"/>
       <c r="J59" s="3"/>
       <c r="K59" s="1"/>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="1"/>
+      <c r="M59" s="1"/>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -2850,8 +3474,10 @@
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
       <c r="K60" s="1"/>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L60" s="1"/>
+      <c r="M60" s="1"/>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A61" s="7" t="s">
         <v>154</v>
       </c>
@@ -2867,8 +3493,10 @@
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
       <c r="K61" s="1"/>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="1"/>
+      <c r="M61" s="1"/>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>155</v>
       </c>
@@ -2877,7 +3505,7 @@
       </c>
       <c r="H62" s="1"/>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>156</v>
       </c>
@@ -2885,12 +3513,12 @@
         <v>169</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>172</v>
       </c>
@@ -2901,12 +3529,12 @@
         <v>178</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.2">
       <c r="G66" s="7" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>161</v>
       </c>
@@ -2914,98 +3542,220 @@
         <v>114</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.2">
       <c r="G68" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:16" ht="46" x14ac:dyDescent="0.2">
       <c r="G69" s="1" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="O69" s="22" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" ht="17" x14ac:dyDescent="0.2">
       <c r="G70" s="1" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="N70" s="18" t="s">
+        <v>228</v>
+      </c>
+      <c r="O70" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="N71" t="s">
+        <v>229</v>
+      </c>
+      <c r="O71" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.2">
       <c r="G72" s="4" t="s">
         <v>131</v>
       </c>
       <c r="H72" s="1"/>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="N72" t="s">
+        <v>230</v>
+      </c>
+      <c r="O72" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.2">
       <c r="G73" s="7" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="N73" t="s">
+        <v>231</v>
+      </c>
+      <c r="O73" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.2">
       <c r="G74" s="1" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="O74" s="1"/>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.2">
       <c r="G75" s="1"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="G76" s="4" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="P76" s="23" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.2">
       <c r="G77" s="7" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="P77" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.2">
       <c r="G78" s="1" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="P78" s="20" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.2">
       <c r="G79" s="1"/>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="P79" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.2">
       <c r="G80" s="4" t="s">
         <v>150</v>
       </c>
       <c r="H80" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="81" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="P80" s="20" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="81" spans="7:16" x14ac:dyDescent="0.2">
       <c r="G81" s="7" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="82" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="P81" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="82" spans="7:16" x14ac:dyDescent="0.2">
       <c r="G82" s="7" t="s">
         <v>140</v>
       </c>
       <c r="H82" s="1"/>
     </row>
-    <row r="83" spans="7:8" x14ac:dyDescent="0.2">
+    <row r="83" spans="7:16" x14ac:dyDescent="0.2">
       <c r="G83" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="85" spans="7:8" x14ac:dyDescent="0.2">
+    <row r="84" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="N84" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="O84" s="13">
+        <v>50</v>
+      </c>
+      <c r="P84" s="13">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="85" spans="7:16" x14ac:dyDescent="0.2">
       <c r="G85" s="4" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="86" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="N85" t="s">
+        <v>236</v>
+      </c>
+      <c r="O85" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="86" spans="7:16" x14ac:dyDescent="0.2">
       <c r="G86" s="7" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="87" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="O86" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="87" spans="7:16" x14ac:dyDescent="0.2">
       <c r="G87" s="1" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="101" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="O87" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="88" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="O88" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="89" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="O89" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="90" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="O90" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="91" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="O91" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="92" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="O92" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="93" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="O93" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="95" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="N95" t="s">
+        <v>237</v>
+      </c>
+      <c r="O95" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="96" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="O96" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="98" spans="7:15" x14ac:dyDescent="0.2">
+      <c r="N98" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="O98" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="101" spans="7:15" x14ac:dyDescent="0.2">
       <c r="G101" s="13"/>
     </row>
   </sheetData>

--- a/Working file.xlsx
+++ b/Working file.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swathirao/Documents/GitHub/DBMS-Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{745DBE0B-6C8C-2340-8C71-8AFE342AE60F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9581BAD-5CD4-F34B-8CC4-0CBCCB26D899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="1" xr2:uid="{FA827ABB-7F19-A44A-951E-8E5375625068}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19500" activeTab="1" xr2:uid="{FA827ABB-7F19-A44A-951E-8E5375625068}"/>
   </bookViews>
   <sheets>
     <sheet name="Tables" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="246">
   <si>
     <t>Airline</t>
   </si>
@@ -773,13 +773,19 @@
   </si>
   <si>
     <t>In raw dataset but not added here because of repeating group</t>
+  </si>
+  <si>
+    <t>Either use Flights.Tail_Number = Airlines.Tail_Number to get Airlines.AirlineID and match with AirlineName.AirlineID to get AirlineName (OR) Manually map AirlineID before upload</t>
+  </si>
+  <si>
+    <t>If using sql join, keep this, else retain only in Flights table</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -865,6 +871,12 @@
       <name val="Helvetica"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9" tint="-0.249977111117893"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -904,7 +916,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -922,9 +934,6 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -939,6 +948,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1547,7 +1560,7 @@
         <v>33</v>
       </c>
       <c r="B27" s="1"/>
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="23" t="s">
         <v>58</v>
       </c>
       <c r="D27" s="1" t="s">
@@ -1560,7 +1573,7 @@
         <v>34</v>
       </c>
       <c r="B28" s="1"/>
-      <c r="C28" s="15"/>
+      <c r="C28" s="23"/>
       <c r="D28" s="1" t="s">
         <v>40</v>
       </c>
@@ -1678,7 +1691,7 @@
         <v>51</v>
       </c>
       <c r="B40" s="1"/>
-      <c r="C40" s="15" t="s">
+      <c r="C40" s="23" t="s">
         <v>58</v>
       </c>
       <c r="D40" s="3" t="s">
@@ -1691,7 +1704,7 @@
         <v>53</v>
       </c>
       <c r="B41" s="1"/>
-      <c r="C41" s="15"/>
+      <c r="C41" s="23"/>
       <c r="D41" s="3" t="s">
         <v>53</v>
       </c>
@@ -2090,6 +2103,7 @@
   <dimension ref="A1:S101"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="8" max="8" width="37.1640625" customWidth="1"/>
     <col min="11" max="11" width="9" customWidth="1"/>
     <col min="12" max="12" width="10.83203125" customWidth="1"/>
     <col min="13" max="13" width="0.1640625" customWidth="1"/>
@@ -2177,7 +2191,7 @@
       <c r="O3" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="P3" s="20" t="s">
+      <c r="P3" s="19" t="s">
         <v>186</v>
       </c>
     </row>
@@ -2204,7 +2218,7 @@
       <c r="O4" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="P4" s="19" t="s">
+      <c r="P4" s="18" t="s">
         <v>187</v>
       </c>
     </row>
@@ -2242,8 +2256,12 @@
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
+      <c r="G6" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>245</v>
+      </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
@@ -2252,7 +2270,7 @@
       <c r="O6" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="P6" s="19" t="s">
+      <c r="P6" s="18" t="s">
         <v>189</v>
       </c>
     </row>
@@ -2336,7 +2354,7 @@
       <c r="O10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P10" s="19" t="s">
+      <c r="P10" s="18" t="s">
         <v>192</v>
       </c>
     </row>
@@ -2398,7 +2416,7 @@
       <c r="O13" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="P13" s="20" t="s">
+      <c r="P13" s="19" t="s">
         <v>200</v>
       </c>
     </row>
@@ -2438,7 +2456,7 @@
       <c r="O15" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="P15" s="19" t="s">
+      <c r="P15" s="18" t="s">
         <v>233</v>
       </c>
     </row>
@@ -2464,7 +2482,7 @@
       <c r="O16" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="P16" s="21" t="s">
+      <c r="P16" s="20" t="s">
         <v>225</v>
       </c>
     </row>
@@ -2489,7 +2507,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>122</v>
       </c>
@@ -2501,6 +2519,9 @@
       <c r="G18" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="H18" s="17" t="s">
+        <v>244</v>
+      </c>
       <c r="J18" s="1"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.2">
@@ -2538,7 +2559,7 @@
       <c r="O20" t="s">
         <v>31</v>
       </c>
-      <c r="P20" s="20" t="s">
+      <c r="P20" s="19" t="s">
         <v>203</v>
       </c>
     </row>
@@ -2926,7 +2947,7 @@
       <c r="O36" t="s">
         <v>60</v>
       </c>
-      <c r="P36" s="20" t="s">
+      <c r="P36" s="19" t="s">
         <v>217</v>
       </c>
     </row>
@@ -2953,7 +2974,7 @@
       <c r="O37" t="s">
         <v>61</v>
       </c>
-      <c r="P37" s="19" t="s">
+      <c r="P37" s="18" t="s">
         <v>218</v>
       </c>
     </row>
@@ -3142,7 +3163,7 @@
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
       <c r="M45" s="1"/>
-      <c r="N45" s="18" t="s">
+      <c r="N45" s="17" t="s">
         <v>224</v>
       </c>
       <c r="O45" t="s">
@@ -3240,14 +3261,6 @@
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
-      <c r="F50" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="G50" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="H50" s="5"/>
-      <c r="I50" s="1"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
@@ -3267,14 +3280,6 @@
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
-      <c r="F51" s="1"/>
-      <c r="G51" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="H51" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
@@ -3294,12 +3299,6 @@
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
-      <c r="F52" s="1"/>
-      <c r="G52" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="H52" s="5"/>
-      <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
@@ -3319,12 +3318,6 @@
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
-      <c r="F53" s="1"/>
-      <c r="G53" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="H53" s="5"/>
-      <c r="I53" s="1"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
@@ -3344,10 +3337,6 @@
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
-      <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
-      <c r="H54" s="1"/>
-      <c r="I54" s="1"/>
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
       <c r="L54" s="1"/>
@@ -3355,7 +3344,7 @@
       <c r="O54" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="P54" s="21" t="s">
+      <c r="P54" s="20" t="s">
         <v>243</v>
       </c>
     </row>
@@ -3364,10 +3353,6 @@
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
-      <c r="F55" s="1"/>
-      <c r="G55" s="1"/>
-      <c r="H55" s="1"/>
-      <c r="I55" s="1"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
       <c r="L55" s="1"/>
@@ -3375,24 +3360,16 @@
       <c r="O55" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="P55" s="21" t="s">
+      <c r="P55" s="20" t="s">
         <v>243</v>
       </c>
-      <c r="S55" s="20"/>
+      <c r="S55" s="19"/>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
-      <c r="F56" s="1"/>
-      <c r="G56" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="I56" s="1"/>
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
       <c r="L56" s="1"/>
@@ -3400,7 +3377,7 @@
       <c r="O56" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="P56" s="21" t="s">
+      <c r="P56" s="20" t="s">
         <v>243</v>
       </c>
     </row>
@@ -3410,11 +3387,13 @@
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
-      <c r="F57" s="1"/>
-      <c r="G57" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="H57" s="1"/>
+      <c r="F57" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="G57" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="H57" s="5"/>
       <c r="I57" s="1"/>
       <c r="K57" s="1"/>
       <c r="L57" s="1"/>
@@ -3422,7 +3401,7 @@
       <c r="O57" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="P57" s="21" t="s">
+      <c r="P57" s="20" t="s">
         <v>243</v>
       </c>
     </row>
@@ -3433,16 +3412,18 @@
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
-      <c r="G58" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="H58" s="1"/>
+      <c r="G58" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="H58" s="5" t="s">
+        <v>163</v>
+      </c>
       <c r="I58" s="1"/>
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
       <c r="M58" s="1"/>
       <c r="O58" s="1"/>
-      <c r="P58" s="21"/>
+      <c r="P58" s="20"/>
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A59" s="1"/>
@@ -3451,10 +3432,10 @@
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
-      <c r="G59" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="H59" s="1"/>
+      <c r="G59" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="H59" s="5"/>
       <c r="I59" s="1"/>
       <c r="J59" s="3"/>
       <c r="K59" s="1"/>
@@ -3468,10 +3449,10 @@
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
-      <c r="G60" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="H60" s="1"/>
+      <c r="G60" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="H60" s="5"/>
       <c r="I60" s="1"/>
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
@@ -3486,9 +3467,7 @@
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
-      <c r="G61" s="1" t="s">
-        <v>112</v>
-      </c>
+      <c r="G61" s="1"/>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
@@ -3500,66 +3479,87 @@
       <c r="A62" t="s">
         <v>155</v>
       </c>
-      <c r="G62" s="1" t="s">
-        <v>126</v>
-      </c>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
       <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>156</v>
       </c>
-      <c r="G63" s="1" t="s">
-        <v>169</v>
-      </c>
+      <c r="F63" s="1"/>
+      <c r="G63" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="I63" s="1"/>
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>157</v>
       </c>
+      <c r="F64" s="1"/>
+      <c r="G64" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>172</v>
       </c>
-      <c r="G65" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="H65" s="1" t="s">
-        <v>178</v>
-      </c>
+      <c r="F65" s="1"/>
+      <c r="G65" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="G66" s="7" t="s">
-        <v>118</v>
-      </c>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>161</v>
       </c>
+      <c r="F67" s="1"/>
       <c r="G67" s="1" t="s">
-        <v>114</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="H67" s="1"/>
+      <c r="I67" s="1"/>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="F68" s="1"/>
       <c r="G68" s="1" t="s">
-        <v>115</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
     </row>
     <row r="69" spans="1:16" ht="46" x14ac:dyDescent="0.2">
       <c r="G69" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="O69" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="H69" s="1"/>
+      <c r="O69" s="21" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="70" spans="1:16" ht="17" x14ac:dyDescent="0.2">
       <c r="G70" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="N70" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="N70" s="17" t="s">
         <v>228</v>
       </c>
       <c r="O70" t="s">
@@ -3576,9 +3576,11 @@
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.2">
       <c r="G72" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="H72" s="1"/>
+        <v>168</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>178</v>
+      </c>
       <c r="N72" t="s">
         <v>230</v>
       </c>
@@ -3588,7 +3590,7 @@
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.2">
       <c r="G73" s="7" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="N73" t="s">
         <v>231</v>
@@ -3599,74 +3601,73 @@
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.2">
       <c r="G74" s="1" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="O74" s="1"/>
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="G75" s="1"/>
+      <c r="G75" s="1" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="76" spans="1:16" ht="51" x14ac:dyDescent="0.2">
-      <c r="G76" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="P76" s="23" t="s">
+      <c r="G76" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="P76" s="22" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="G77" s="7" t="s">
-        <v>140</v>
+      <c r="G77" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="P77" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="G78" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="P78" s="20" t="s">
+      <c r="P78" s="19" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="G79" s="1"/>
+      <c r="G79" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="H79" s="1"/>
       <c r="P79" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="G80" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="H80" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="P80" s="20" t="s">
+      <c r="G80" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="P80" s="19" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="81" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G81" s="7" t="s">
-        <v>135</v>
+      <c r="G81" s="1" t="s">
+        <v>132</v>
       </c>
       <c r="P81" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="82" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G82" s="7" t="s">
+      <c r="G82" s="1"/>
+    </row>
+    <row r="83" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="G83" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="84" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="G84" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="H82" s="1"/>
-    </row>
-    <row r="83" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G83" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="84" spans="7:16" x14ac:dyDescent="0.2">
       <c r="N84" s="13" t="s">
         <v>232</v>
       </c>
@@ -3678,8 +3679,8 @@
       </c>
     </row>
     <row r="85" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G85" s="4" t="s">
-        <v>144</v>
+      <c r="G85" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="N85" t="s">
         <v>236</v>
@@ -3689,32 +3690,43 @@
       </c>
     </row>
     <row r="86" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G86" s="7" t="s">
-        <v>145</v>
-      </c>
+      <c r="G86" s="1"/>
       <c r="O86" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="87" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G87" s="1" t="s">
-        <v>146</v>
+      <c r="G87" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>166</v>
       </c>
       <c r="O87" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="88" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="G88" s="7" t="s">
+        <v>135</v>
+      </c>
       <c r="O88" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="89" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="G89" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="H89" s="1"/>
       <c r="O89" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="90" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="G90" s="1" t="s">
+        <v>151</v>
+      </c>
       <c r="O90" t="s">
         <v>144</v>
       </c>
@@ -3725,13 +3737,24 @@
       </c>
     </row>
     <row r="92" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="G92" s="4" t="s">
+        <v>144</v>
+      </c>
       <c r="O92" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="93" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="G93" s="7" t="s">
+        <v>145</v>
+      </c>
       <c r="O93" t="s">
         <v>235</v>
+      </c>
+    </row>
+    <row r="94" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="G94" s="1" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="95" spans="7:16" x14ac:dyDescent="0.2">

--- a/Working file.xlsx
+++ b/Working file.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swathirao/Documents/GitHub/DBMS-Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9581BAD-5CD4-F34B-8CC4-0CBCCB26D899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59DBF2FA-0726-6643-849C-254A3CA58F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19500" activeTab="1" xr2:uid="{FA827ABB-7F19-A44A-951E-8E5375625068}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="2" xr2:uid="{FA827ABB-7F19-A44A-951E-8E5375625068}"/>
   </bookViews>
   <sheets>
     <sheet name="Tables" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Schema definition" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="278">
   <si>
     <t>Airline</t>
   </si>
@@ -779,6 +780,102 @@
   </si>
   <si>
     <t>If using sql join, keep this, else retain only in Flights table</t>
+  </si>
+  <si>
+    <t>MySQL column type</t>
+  </si>
+  <si>
+    <t>SMALLINT</t>
+  </si>
+  <si>
+    <t>Can we have this in words?</t>
+  </si>
+  <si>
+    <t>TINYINT</t>
+  </si>
+  <si>
+    <t>INT</t>
+  </si>
+  <si>
+    <t>VARCHAR(7)</t>
+  </si>
+  <si>
+    <t>VARCHAR(5)</t>
+  </si>
+  <si>
+    <t>VARCHAR(8)</t>
+  </si>
+  <si>
+    <t>VARCHAR(50)</t>
+  </si>
+  <si>
+    <t>Columns from raw data</t>
+  </si>
+  <si>
+    <t>STATE_FIPS</t>
+  </si>
+  <si>
+    <t>AIRPORT_ID</t>
+  </si>
+  <si>
+    <t>CITY_NAME</t>
+  </si>
+  <si>
+    <t>STATE_NM</t>
+  </si>
+  <si>
+    <t>DIV_AIRPORT_LANDINGS</t>
+  </si>
+  <si>
+    <t>DIV_REACHED_DEST</t>
+  </si>
+  <si>
+    <t>DIV_ACTUAL_ELAPSED_TIME</t>
+  </si>
+  <si>
+    <t>DIV_ARR_DELAY</t>
+  </si>
+  <si>
+    <t>DIV_DISTANCE</t>
+  </si>
+  <si>
+    <t>DIV_AIRPORT</t>
+  </si>
+  <si>
+    <t>DIV_WHEELS_ON</t>
+  </si>
+  <si>
+    <t>DIV_WHEELS_OFF</t>
+  </si>
+  <si>
+    <t>DIV_TOTAL_GTIME</t>
+  </si>
+  <si>
+    <t>SMALLINT SIGNED</t>
+  </si>
+  <si>
+    <t>SMALLINT UNSIGNED</t>
+  </si>
+  <si>
+    <t>default is signed</t>
+  </si>
+  <si>
+    <t>need to have only positive values</t>
+  </si>
+  <si>
+    <t>Indicator</t>
+  </si>
+  <si>
+    <t>ACTUAL_ELAPSED_TIME</t>
+  </si>
+  <si>
+    <t>TINY</t>
+  </si>
+  <si>
+    <t>DIV_AIRPORT_ID</t>
+  </si>
+  <si>
+    <t>VARCHAR(20)</t>
   </si>
 </sst>
 </file>
@@ -916,7 +1013,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -948,10 +1045,11 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1560,7 +1658,7 @@
         <v>33</v>
       </c>
       <c r="B27" s="1"/>
-      <c r="C27" s="23" t="s">
+      <c r="C27" s="24" t="s">
         <v>58</v>
       </c>
       <c r="D27" s="1" t="s">
@@ -1573,7 +1671,7 @@
         <v>34</v>
       </c>
       <c r="B28" s="1"/>
-      <c r="C28" s="23"/>
+      <c r="C28" s="24"/>
       <c r="D28" s="1" t="s">
         <v>40</v>
       </c>
@@ -1691,7 +1789,7 @@
         <v>51</v>
       </c>
       <c r="B40" s="1"/>
-      <c r="C40" s="23" t="s">
+      <c r="C40" s="24" t="s">
         <v>58</v>
       </c>
       <c r="D40" s="3" t="s">
@@ -1704,7 +1802,7 @@
         <v>53</v>
       </c>
       <c r="B41" s="1"/>
-      <c r="C41" s="23"/>
+      <c r="C41" s="24"/>
       <c r="D41" s="3" t="s">
         <v>53</v>
       </c>
@@ -2110,7 +2208,7 @@
     <col min="14" max="14" width="33" customWidth="1"/>
     <col min="15" max="15" width="22.33203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="30.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.2">
@@ -2167,6 +2265,9 @@
       <c r="P2" t="s">
         <v>183</v>
       </c>
+      <c r="R2" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -2194,6 +2295,9 @@
       <c r="P3" s="19" t="s">
         <v>186</v>
       </c>
+      <c r="R3" s="19" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -2219,6 +2323,9 @@
         <v>136</v>
       </c>
       <c r="P4" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="R4" s="18" t="s">
         <v>187</v>
       </c>
     </row>
@@ -2246,6 +2353,9 @@
       <c r="P5" t="s">
         <v>188</v>
       </c>
+      <c r="R5" t="s">
+        <v>188</v>
+      </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -2256,7 +2366,7 @@
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
-      <c r="G6" s="24" t="s">
+      <c r="G6" s="23" t="s">
         <v>3</v>
       </c>
       <c r="H6" s="1" t="s">
@@ -2271,6 +2381,9 @@
         <v>118</v>
       </c>
       <c r="P6" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="R6" s="18" t="s">
         <v>189</v>
       </c>
     </row>
@@ -2309,6 +2422,9 @@
       <c r="P8" t="s">
         <v>190</v>
       </c>
+      <c r="R8" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
@@ -2333,6 +2449,9 @@
       <c r="P9" t="s">
         <v>191</v>
       </c>
+      <c r="R9" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
@@ -2357,6 +2476,9 @@
       <c r="P10" s="18" t="s">
         <v>192</v>
       </c>
+      <c r="R10" s="18" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
@@ -2377,6 +2499,9 @@
         <v>3</v>
       </c>
       <c r="P11" t="s">
+        <v>193</v>
+      </c>
+      <c r="R11" t="s">
         <v>193</v>
       </c>
     </row>
@@ -2485,8 +2610,11 @@
       <c r="P16" s="20" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R16" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>121</v>
       </c>
@@ -2507,7 +2635,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="85" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>122</v>
       </c>
@@ -2524,7 +2652,7 @@
       </c>
       <c r="J18" s="1"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>123</v>
       </c>
@@ -2539,7 +2667,7 @@
       <c r="H19" s="1"/>
       <c r="J19" s="1"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>124</v>
       </c>
@@ -2562,8 +2690,11 @@
       <c r="P20" s="19" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R20" s="19" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>31</v>
       </c>
@@ -2586,8 +2717,11 @@
       <c r="P21" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R21" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>32</v>
       </c>
@@ -2607,8 +2741,11 @@
       <c r="P22" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R22" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>34</v>
       </c>
@@ -2631,8 +2768,11 @@
       <c r="P23" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R23" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>35</v>
       </c>
@@ -2656,8 +2796,11 @@
       <c r="P24" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R24" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>38</v>
       </c>
@@ -2681,8 +2824,11 @@
       <c r="P25" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R25" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>39</v>
       </c>
@@ -2708,8 +2854,11 @@
       <c r="P26" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R26" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>125</v>
       </c>
@@ -2735,8 +2884,11 @@
       <c r="P27" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R27" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>48</v>
       </c>
@@ -2760,8 +2912,11 @@
       <c r="P28" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R28" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>49</v>
       </c>
@@ -2785,8 +2940,11 @@
       <c r="P29" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R29" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
         <v>50</v>
       </c>
@@ -2810,8 +2968,11 @@
       <c r="P30" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R30" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>53</v>
       </c>
@@ -2835,8 +2996,11 @@
       <c r="P31" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R31" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
         <v>54</v>
       </c>
@@ -2860,8 +3024,11 @@
       <c r="P32" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R32" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>60</v>
       </c>
@@ -2885,8 +3052,11 @@
       <c r="P33" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R33" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
         <v>61</v>
       </c>
@@ -2905,7 +3075,7 @@
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>62</v>
       </c>
@@ -2924,7 +3094,7 @@
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
         <v>77</v>
       </c>
@@ -2950,8 +3120,11 @@
       <c r="P36" s="19" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R36" s="19" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
         <v>78</v>
       </c>
@@ -2977,8 +3150,11 @@
       <c r="P37" s="18" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R37" s="18" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
         <v>79</v>
       </c>
@@ -3001,8 +3177,11 @@
       <c r="P38" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R38" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
         <v>81</v>
       </c>
@@ -3023,7 +3202,7 @@
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
         <v>65</v>
       </c>
@@ -3049,8 +3228,11 @@
       <c r="P40" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R40" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
         <v>67</v>
       </c>
@@ -3073,8 +3255,11 @@
       <c r="P41" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R41" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
         <v>68</v>
       </c>
@@ -3100,8 +3285,11 @@
       <c r="P42" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R42" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
         <v>69</v>
       </c>
@@ -3125,8 +3313,11 @@
       <c r="P43" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R43" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
         <v>70</v>
       </c>
@@ -3145,7 +3336,7 @@
       <c r="L44" s="1"/>
       <c r="M44" s="1"/>
     </row>
-    <row r="45" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:18" ht="34" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
         <v>106</v>
       </c>
@@ -3170,7 +3361,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
         <v>107</v>
       </c>
@@ -3195,7 +3386,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
         <v>84</v>
       </c>
@@ -3216,7 +3407,7 @@
       <c r="L47" s="1"/>
       <c r="M47" s="1"/>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
         <v>86</v>
       </c>
@@ -3252,6 +3443,9 @@
       <c r="P49" t="s">
         <v>84</v>
       </c>
+      <c r="R49" t="s">
+        <v>260</v>
+      </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
@@ -3271,6 +3465,9 @@
       <c r="P50" t="s">
         <v>86</v>
       </c>
+      <c r="R50" t="s">
+        <v>261</v>
+      </c>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
@@ -3290,6 +3487,9 @@
       <c r="P51" t="s">
         <v>88</v>
       </c>
+      <c r="R51" t="s">
+        <v>262</v>
+      </c>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
@@ -3309,6 +3509,9 @@
       <c r="P52" t="s">
         <v>90</v>
       </c>
+      <c r="R52" t="s">
+        <v>263</v>
+      </c>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
@@ -3328,6 +3531,9 @@
       <c r="P53" t="s">
         <v>227</v>
       </c>
+      <c r="R53" t="s">
+        <v>264</v>
+      </c>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
@@ -3346,6 +3552,9 @@
       </c>
       <c r="P54" s="20" t="s">
         <v>243</v>
+      </c>
+      <c r="R54" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.2">
@@ -3363,6 +3572,9 @@
       <c r="P55" s="20" t="s">
         <v>243</v>
       </c>
+      <c r="R55" t="s">
+        <v>266</v>
+      </c>
       <c r="S55" s="19"/>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.2">
@@ -3380,6 +3592,9 @@
       <c r="P56" s="20" t="s">
         <v>243</v>
       </c>
+      <c r="R56" t="s">
+        <v>267</v>
+      </c>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A57" s="1"/>
@@ -3403,6 +3618,9 @@
       </c>
       <c r="P57" s="20" t="s">
         <v>243</v>
+      </c>
+      <c r="R57" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.2">
@@ -3784,4 +4002,425 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91E5C0D5-7C48-D049-AD0D-6AA6E46E02BD}">
+  <dimension ref="A1:C56"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="41.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="C3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="B4" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>188</v>
+      </c>
+      <c r="C5" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="18" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>190</v>
+      </c>
+      <c r="B8" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>191</v>
+      </c>
+      <c r="B9" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="18" t="s">
+        <v>192</v>
+      </c>
+      <c r="B10" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>193</v>
+      </c>
+      <c r="B11" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="19" t="s">
+        <v>257</v>
+      </c>
+      <c r="B13" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>201</v>
+      </c>
+      <c r="B14" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="18" t="s">
+        <v>258</v>
+      </c>
+      <c r="B15" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="B16" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>259</v>
+      </c>
+      <c r="B17" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="B19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>204</v>
+      </c>
+      <c r="B20" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>205</v>
+      </c>
+      <c r="B21" t="s">
+        <v>269</v>
+      </c>
+      <c r="C21" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>206</v>
+      </c>
+      <c r="B22" t="s">
+        <v>270</v>
+      </c>
+      <c r="C22" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>207</v>
+      </c>
+      <c r="B23" t="s">
+        <v>249</v>
+      </c>
+      <c r="C23" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>208</v>
+      </c>
+      <c r="B24" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>209</v>
+      </c>
+      <c r="B25" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>210</v>
+      </c>
+      <c r="B26" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>211</v>
+      </c>
+      <c r="B27" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>212</v>
+      </c>
+      <c r="B28" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>213</v>
+      </c>
+      <c r="B29" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>214</v>
+      </c>
+      <c r="B30" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>215</v>
+      </c>
+      <c r="B31" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>216</v>
+      </c>
+      <c r="B32" t="s">
+        <v>249</v>
+      </c>
+      <c r="C32" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="B34" t="s">
+        <v>249</v>
+      </c>
+      <c r="C34" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="B35" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>219</v>
+      </c>
+      <c r="B36" t="s">
+        <v>249</v>
+      </c>
+      <c r="C36" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>220</v>
+      </c>
+      <c r="B38" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>274</v>
+      </c>
+      <c r="B39" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>222</v>
+      </c>
+      <c r="B40" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>223</v>
+      </c>
+      <c r="B41" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>260</v>
+      </c>
+      <c r="B43" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>261</v>
+      </c>
+      <c r="B44" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>262</v>
+      </c>
+      <c r="B45" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>263</v>
+      </c>
+      <c r="B46" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>264</v>
+      </c>
+      <c r="B47" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>276</v>
+      </c>
+      <c r="B48" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>266</v>
+      </c>
+      <c r="B49" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>267</v>
+      </c>
+      <c r="B50" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>268</v>
+      </c>
+      <c r="B51" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>135</v>
+      </c>
+      <c r="B53" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>141</v>
+      </c>
+      <c r="B54" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B55" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B56" t="s">
+        <v>277</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Working file.xlsx
+++ b/Working file.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swathirao/Documents/GitHub/DBMS-Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59DBF2FA-0726-6643-849C-254A3CA58F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C0567BE-BFD2-0A44-A110-2CD8615206F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="2" xr2:uid="{FA827ABB-7F19-A44A-951E-8E5375625068}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19620" activeTab="2" xr2:uid="{FA827ABB-7F19-A44A-951E-8E5375625068}"/>
   </bookViews>
   <sheets>
     <sheet name="Tables" sheetId="1" r:id="rId1"/>
@@ -797,9 +797,6 @@
     <t>INT</t>
   </si>
   <si>
-    <t>VARCHAR(7)</t>
-  </si>
-  <si>
     <t>VARCHAR(5)</t>
   </si>
   <si>
@@ -876,13 +873,16 @@
   </si>
   <si>
     <t>VARCHAR(20)</t>
+  </si>
+  <si>
+    <t>TIME</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -974,6 +974,13 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1049,7 +1056,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2611,7 +2618,7 @@
         <v>225</v>
       </c>
       <c r="R16" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.2">
@@ -3256,7 +3263,7 @@
         <v>221</v>
       </c>
       <c r="R41" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.2">
@@ -3444,7 +3451,7 @@
         <v>84</v>
       </c>
       <c r="R49" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.2">
@@ -3466,7 +3473,7 @@
         <v>86</v>
       </c>
       <c r="R50" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.2">
@@ -3488,7 +3495,7 @@
         <v>88</v>
       </c>
       <c r="R51" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.2">
@@ -3510,7 +3517,7 @@
         <v>90</v>
       </c>
       <c r="R52" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.2">
@@ -3532,7 +3539,7 @@
         <v>227</v>
       </c>
       <c r="R53" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.2">
@@ -3554,7 +3561,7 @@
         <v>243</v>
       </c>
       <c r="R54" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.2">
@@ -3573,7 +3580,7 @@
         <v>243</v>
       </c>
       <c r="R55" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="S55" s="19"/>
     </row>
@@ -3593,7 +3600,7 @@
         <v>243</v>
       </c>
       <c r="R56" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.2">
@@ -3620,7 +3627,7 @@
         <v>243</v>
       </c>
       <c r="R57" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.2">
@@ -4015,7 +4022,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>246</v>
@@ -4071,7 +4078,7 @@
         <v>191</v>
       </c>
       <c r="B9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -4079,7 +4086,7 @@
         <v>192</v>
       </c>
       <c r="B10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -4087,12 +4094,12 @@
         <v>193</v>
       </c>
       <c r="B11" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="19" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B13" t="s">
         <v>250</v>
@@ -4103,20 +4110,20 @@
         <v>201</v>
       </c>
       <c r="B14" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="18" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="25" t="s">
-        <v>256</v>
+      <c r="A16" t="s">
+        <v>255</v>
       </c>
       <c r="B16" t="s">
         <v>249</v>
@@ -4124,10 +4131,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B17" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -4135,7 +4142,7 @@
         <v>203</v>
       </c>
       <c r="B19" t="s">
-        <v>251</v>
+        <v>277</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -4143,7 +4150,7 @@
         <v>204</v>
       </c>
       <c r="B20" t="s">
-        <v>251</v>
+        <v>277</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -4151,10 +4158,10 @@
         <v>205</v>
       </c>
       <c r="B21" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -4162,10 +4169,10 @@
         <v>206</v>
       </c>
       <c r="B22" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C22" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -4176,7 +4183,7 @@
         <v>249</v>
       </c>
       <c r="C23" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -4184,7 +4191,7 @@
         <v>208</v>
       </c>
       <c r="B24" t="s">
-        <v>251</v>
+        <v>277</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -4192,7 +4199,7 @@
         <v>209</v>
       </c>
       <c r="B25" t="s">
-        <v>251</v>
+        <v>277</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -4200,7 +4207,7 @@
         <v>210</v>
       </c>
       <c r="B26" t="s">
-        <v>251</v>
+        <v>277</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -4208,7 +4215,7 @@
         <v>211</v>
       </c>
       <c r="B27" t="s">
-        <v>251</v>
+        <v>277</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -4216,7 +4223,7 @@
         <v>212</v>
       </c>
       <c r="B28" t="s">
-        <v>251</v>
+        <v>277</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -4224,7 +4231,7 @@
         <v>213</v>
       </c>
       <c r="B29" t="s">
-        <v>251</v>
+        <v>277</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -4232,7 +4239,7 @@
         <v>214</v>
       </c>
       <c r="B30" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
@@ -4240,7 +4247,7 @@
         <v>215</v>
       </c>
       <c r="B31" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -4251,7 +4258,7 @@
         <v>249</v>
       </c>
       <c r="C32" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -4262,7 +4269,7 @@
         <v>249</v>
       </c>
       <c r="C34" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -4281,7 +4288,7 @@
         <v>249</v>
       </c>
       <c r="C36" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
@@ -4289,15 +4296,15 @@
         <v>220</v>
       </c>
       <c r="B38" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B39" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
@@ -4305,7 +4312,7 @@
         <v>222</v>
       </c>
       <c r="B40" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
@@ -4318,39 +4325,39 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B43" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B44" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B45" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B46" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B47" t="s">
         <v>250</v>
@@ -4358,7 +4365,7 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B48" t="s">
         <v>250</v>
@@ -4366,26 +4373,26 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>266</v>
-      </c>
-      <c r="B49" t="s">
-        <v>251</v>
+        <v>265</v>
+      </c>
+      <c r="B49" s="25" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>267</v>
-      </c>
-      <c r="B50" t="s">
-        <v>251</v>
+        <v>266</v>
+      </c>
+      <c r="B50" s="25" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B51" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
@@ -4417,7 +4424,7 @@
         <v>146</v>
       </c>
       <c r="B56" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>

--- a/Working file.xlsx
+++ b/Working file.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swathirao/Documents/GitHub/DBMS-Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C0567BE-BFD2-0A44-A110-2CD8615206F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16BE2CDA-E262-AD43-BF13-20A317C8E02C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19620" activeTab="2" xr2:uid="{FA827ABB-7F19-A44A-951E-8E5375625068}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19620" activeTab="1" xr2:uid="{FA827ABB-7F19-A44A-951E-8E5375625068}"/>
   </bookViews>
   <sheets>
     <sheet name="Tables" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="300">
   <si>
     <t>Airline</t>
   </si>
@@ -876,6 +876,72 @@
   </si>
   <si>
     <t>TIME</t>
+  </si>
+  <si>
+    <t>Sta</t>
+  </si>
+  <si>
+    <t>STATE_ABR</t>
+  </si>
+  <si>
+    <t>DLEAY_ID</t>
+  </si>
+  <si>
+    <t>NAME</t>
+  </si>
+  <si>
+    <t>FLIGHT_ID</t>
+  </si>
+  <si>
+    <t>DIVERSION_NUMBER</t>
+  </si>
+  <si>
+    <t>MINUTES</t>
+  </si>
+  <si>
+    <t>DESCRIPTION</t>
+  </si>
+  <si>
+    <t>TimePeriod</t>
+  </si>
+  <si>
+    <t>PK</t>
+  </si>
+  <si>
+    <t>AIRLINE_ID</t>
+  </si>
+  <si>
+    <t>ORIGIN_AIRPORT_ID</t>
+  </si>
+  <si>
+    <t>DEST_AIRPORT_ID</t>
+  </si>
+  <si>
+    <t>Routes</t>
+  </si>
+  <si>
+    <t>ROUTE_ID</t>
+  </si>
+  <si>
+    <t>FlightPerformance</t>
+  </si>
+  <si>
+    <t>DELAY_ID</t>
+  </si>
+  <si>
+    <t>StateNames</t>
+  </si>
+  <si>
+    <t>IATA_CODE</t>
+  </si>
+  <si>
+    <t>Mapping it manually</t>
+  </si>
+  <si>
+    <t>Update manually to weekday names</t>
+  </si>
+  <si>
+    <t>PK/FK</t>
   </si>
 </sst>
 </file>
@@ -1020,7 +1086,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1053,10 +1119,35 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1665,7 +1756,7 @@
         <v>33</v>
       </c>
       <c r="B27" s="1"/>
-      <c r="C27" s="24" t="s">
+      <c r="C27" s="25" t="s">
         <v>58</v>
       </c>
       <c r="D27" s="1" t="s">
@@ -1678,7 +1769,7 @@
         <v>34</v>
       </c>
       <c r="B28" s="1"/>
-      <c r="C28" s="24"/>
+      <c r="C28" s="25"/>
       <c r="D28" s="1" t="s">
         <v>40</v>
       </c>
@@ -1796,7 +1887,7 @@
         <v>51</v>
       </c>
       <c r="B40" s="1"/>
-      <c r="C40" s="24" t="s">
+      <c r="C40" s="25" t="s">
         <v>58</v>
       </c>
       <c r="D40" s="3" t="s">
@@ -1809,7 +1900,7 @@
         <v>53</v>
       </c>
       <c r="B41" s="1"/>
-      <c r="C41" s="24"/>
+      <c r="C41" s="25"/>
       <c r="D41" s="3" t="s">
         <v>53</v>
       </c>
@@ -2205,7 +2296,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CA334EF-316D-FA44-936F-23AB3782E682}">
-  <dimension ref="A1:S101"/>
+  <dimension ref="A1:AB114"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="8" max="8" width="37.1640625" customWidth="1"/>
@@ -2215,10 +2306,12 @@
     <col min="14" max="14" width="33" customWidth="1"/>
     <col min="15" max="15" width="22.33203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="30.1640625" customWidth="1"/>
+    <col min="17" max="17" width="83.83203125" customWidth="1"/>
+    <col min="18" max="18" width="22.5" customWidth="1"/>
+    <col min="26" max="26" width="17.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
         <v>167</v>
       </c>
@@ -2246,7 +2339,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>114</v>
       </c>
@@ -2275,8 +2368,11 @@
       <c r="R2" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="T2" s="27" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>115</v>
       </c>
@@ -2305,8 +2401,9 @@
       <c r="R3" s="19" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="T3" s="27"/>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>116</v>
       </c>
@@ -2335,8 +2432,9 @@
       <c r="R4" s="18" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="T4" s="27"/>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>117</v>
       </c>
@@ -2363,8 +2461,12 @@
       <c r="R5" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="T5" s="27"/>
+      <c r="W5" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>118</v>
       </c>
@@ -2393,103 +2495,111 @@
       <c r="R6" s="18" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="S6" t="s">
+        <v>287</v>
+      </c>
+      <c r="T6" s="27"/>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
+      <c r="G7" s="23"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="18"/>
+      <c r="R7" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="T7" s="28"/>
+      <c r="W7" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
-      <c r="G8" s="4" t="s">
-        <v>8</v>
-      </c>
+      <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
-      <c r="O8" t="s">
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
         <v>1</v>
-      </c>
-      <c r="P8" t="s">
-        <v>190</v>
-      </c>
-      <c r="R8" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
-      <c r="G9" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>142</v>
-      </c>
+      <c r="G9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
-      <c r="O9" s="3" t="s">
-        <v>2</v>
+      <c r="O9" t="s">
+        <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="R9" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+        <v>190</v>
+      </c>
+      <c r="S9" t="s">
+        <v>287</v>
+      </c>
+      <c r="T9" s="31" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
-      <c r="G10" s="1" t="s">
-        <v>133</v>
+      <c r="G10" s="7" t="s">
+        <v>128</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>64</v>
+        <v>142</v>
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="O10" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="P10" t="s">
+        <v>191</v>
+      </c>
+      <c r="R10" t="s">
+        <v>191</v>
+      </c>
+      <c r="T10" s="31"/>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
         <v>5</v>
-      </c>
-      <c r="P10" s="18" t="s">
-        <v>192</v>
-      </c>
-      <c r="R10" s="18" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
-        <v>119</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -2497,24 +2607,25 @@
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="H11" s="1"/>
+        <v>133</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>64</v>
+      </c>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="O11" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P11" t="s">
-        <v>193</v>
-      </c>
-      <c r="R11" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="P11" s="18" t="s">
+        <v>192</v>
+      </c>
+      <c r="R11" s="34"/>
+      <c r="T11" s="29"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>15</v>
+        <v>119</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -2522,15 +2633,23 @@
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1" t="s">
-        <v>129</v>
+        <v>162</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" t="s">
+        <v>193</v>
+      </c>
+      <c r="R12" s="35"/>
+      <c r="T12" s="29"/>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -2538,113 +2657,129 @@
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>147</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
-      <c r="O13" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="P13" s="19" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
+      <c r="G14" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="I14" s="1"/>
       <c r="J14" s="1"/>
-      <c r="O14" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="P14" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="P14" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="R14" t="s">
+        <v>256</v>
+      </c>
+      <c r="S14" t="s">
+        <v>287</v>
+      </c>
+      <c r="T14" s="27" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
-      <c r="G15" s="4" t="s">
-        <v>80</v>
-      </c>
+      <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="J15" s="1"/>
       <c r="O15" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="P15" s="18" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+        <v>194</v>
+      </c>
+      <c r="P15" t="s">
+        <v>201</v>
+      </c>
+      <c r="R15" t="s">
+        <v>296</v>
+      </c>
+      <c r="T15" s="27"/>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
-      <c r="G16" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>143</v>
-      </c>
+      <c r="G16" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="H16" s="1"/>
       <c r="J16" s="1"/>
-      <c r="N16" t="s">
-        <v>195</v>
-      </c>
       <c r="O16" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="P16" s="20" t="s">
-        <v>225</v>
+        <v>129</v>
+      </c>
+      <c r="P16" s="18" t="s">
+        <v>233</v>
       </c>
       <c r="R16" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
+        <v>257</v>
+      </c>
+      <c r="T16" s="27"/>
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
-      <c r="G17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H17" s="1"/>
+      <c r="G17" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>143</v>
+      </c>
       <c r="J17" s="1"/>
+      <c r="N17" t="s">
+        <v>195</v>
+      </c>
       <c r="O17" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="P17" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" ht="85" x14ac:dyDescent="0.2">
+        <v>278</v>
+      </c>
+      <c r="P17" s="20" t="s">
+        <v>225</v>
+      </c>
+      <c r="R17" t="s">
+        <v>279</v>
+      </c>
+      <c r="S17" t="s">
+        <v>147</v>
+      </c>
+      <c r="T17" s="27"/>
+    </row>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -2652,31 +2787,37 @@
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H18" s="17" t="s">
-        <v>244</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="H18" s="1"/>
       <c r="J18" s="1"/>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="O18" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="P18" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28" ht="85" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
-      <c r="G19" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="H19" s="1"/>
+      <c r="G19" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H19" s="17" t="s">
+        <v>244</v>
+      </c>
       <c r="J19" s="1"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -2684,26 +2825,32 @@
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="I20" s="1"/>
+        <v>118</v>
+      </c>
+      <c r="H20" s="1"/>
       <c r="J20" s="1"/>
-      <c r="O20" t="s">
-        <v>31</v>
-      </c>
-      <c r="P20" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="R20" s="19" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R20" t="s">
+        <v>282</v>
+      </c>
+      <c r="S20" t="s">
+        <v>299</v>
+      </c>
+      <c r="T20" s="32" t="s">
+        <v>293</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>282</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>287</v>
+      </c>
+      <c r="AB20" s="30" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>31</v>
+        <v>124</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -2711,7 +2858,7 @@
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>147</v>
@@ -2719,69 +2866,87 @@
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="O21" t="s">
-        <v>32</v>
-      </c>
-      <c r="P21" t="s">
-        <v>204</v>
-      </c>
-      <c r="R21" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+      <c r="P21" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="R21" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="T21" s="32"/>
+      <c r="Z21" t="s">
+        <v>192</v>
+      </c>
+      <c r="AB21" s="30"/>
+    </row>
+    <row r="22" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
-      <c r="G22" t="s">
-        <v>81</v>
+      <c r="G22" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>147</v>
       </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="O22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P22" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="R22" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
+        <v>204</v>
+      </c>
+      <c r="T22" s="32"/>
+      <c r="Z22" t="s">
+        <v>193</v>
+      </c>
+      <c r="AB22" s="30"/>
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
-      <c r="G23" s="3" t="s">
-        <v>31</v>
+      <c r="G23" t="s">
+        <v>81</v>
       </c>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
       <c r="O23" t="s">
+        <v>33</v>
+      </c>
+      <c r="P23" t="s">
+        <v>205</v>
+      </c>
+      <c r="R23" t="s">
+        <v>205</v>
+      </c>
+      <c r="T23" s="32"/>
+      <c r="Z23" t="s">
+        <v>288</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>147</v>
+      </c>
+      <c r="AB23" s="30"/>
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A24" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="P23" t="s">
-        <v>206</v>
-      </c>
-      <c r="R23" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A24" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -2789,35 +2954,42 @@
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H24" s="1"/>
+        <v>31</v>
+      </c>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
       <c r="O24" t="s">
+        <v>34</v>
+      </c>
+      <c r="P24" t="s">
+        <v>206</v>
+      </c>
+      <c r="R24" t="s">
+        <v>206</v>
+      </c>
+      <c r="T24" s="32"/>
+      <c r="Z24" t="s">
+        <v>292</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>147</v>
+      </c>
+      <c r="AB24" s="30"/>
+    </row>
+    <row r="25" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A25" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="P24" t="s">
-        <v>207</v>
-      </c>
-      <c r="R24" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A25" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
-      <c r="G25" s="1" t="s">
-        <v>33</v>
+      <c r="G25" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
@@ -2826,48 +2998,59 @@
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
       <c r="O25" t="s">
+        <v>35</v>
+      </c>
+      <c r="P25" t="s">
+        <v>207</v>
+      </c>
+      <c r="R25" t="s">
+        <v>207</v>
+      </c>
+      <c r="T25" s="32"/>
+      <c r="Z25" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>147</v>
+      </c>
+      <c r="AB25" s="30"/>
+    </row>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A26" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="P25" t="s">
-        <v>208</v>
-      </c>
-      <c r="R25" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A26" s="3" t="s">
-        <v>39</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
-      <c r="G26" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>158</v>
-      </c>
+      <c r="G26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
       <c r="O26" t="s">
+        <v>38</v>
+      </c>
+      <c r="P26" t="s">
+        <v>208</v>
+      </c>
+      <c r="R26" t="s">
+        <v>208</v>
+      </c>
+      <c r="T26" s="32"/>
+      <c r="Z26" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="AB26" s="30"/>
+    </row>
+    <row r="27" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A27" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="P26" t="s">
-        <v>209</v>
-      </c>
-      <c r="R26" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A27" s="3" t="s">
-        <v>125</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -2875,7 +3058,7 @@
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>158</v>
@@ -2886,46 +3069,55 @@
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
       <c r="O27" t="s">
+        <v>39</v>
+      </c>
+      <c r="P27" t="s">
+        <v>209</v>
+      </c>
+      <c r="R27" t="s">
+        <v>209</v>
+      </c>
+      <c r="T27" s="32"/>
+      <c r="Z27" t="s">
+        <v>219</v>
+      </c>
+      <c r="AB27" s="30"/>
+    </row>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A28" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="P27" t="s">
-        <v>210</v>
-      </c>
-      <c r="R27" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A28" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
-      <c r="G28" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H28" s="1"/>
+      <c r="G28" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
       <c r="O28" t="s">
+        <v>125</v>
+      </c>
+      <c r="P28" t="s">
+        <v>210</v>
+      </c>
+      <c r="R28" t="s">
+        <v>210</v>
+      </c>
+      <c r="T28" s="32"/>
+      <c r="AB28" s="30"/>
+    </row>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A29" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="P28" t="s">
-        <v>211</v>
-      </c>
-      <c r="R28" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A29" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -2933,7 +3125,7 @@
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -2942,18 +3134,19 @@
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
       <c r="O29" t="s">
+        <v>48</v>
+      </c>
+      <c r="P29" t="s">
+        <v>211</v>
+      </c>
+      <c r="R29" t="s">
+        <v>211</v>
+      </c>
+      <c r="T29" s="32"/>
+    </row>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A30" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="P29" t="s">
-        <v>212</v>
-      </c>
-      <c r="R29" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A30" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -2961,7 +3154,7 @@
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="3" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
@@ -2970,18 +3163,19 @@
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
       <c r="O30" t="s">
+        <v>49</v>
+      </c>
+      <c r="P30" t="s">
+        <v>212</v>
+      </c>
+      <c r="R30" t="s">
+        <v>212</v>
+      </c>
+      <c r="T30" s="32"/>
+    </row>
+    <row r="31" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A31" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="P30" t="s">
-        <v>213</v>
-      </c>
-      <c r="R30" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A31" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -2989,7 +3183,7 @@
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="3" t="s">
-        <v>125</v>
+        <v>79</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -2998,18 +3192,19 @@
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
       <c r="O31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P31" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="R31" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
+        <v>213</v>
+      </c>
+      <c r="T31" s="32"/>
+    </row>
+    <row r="32" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -3017,7 +3212,7 @@
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="3" t="s">
-        <v>48</v>
+        <v>125</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -3026,18 +3221,31 @@
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
       <c r="O32" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="P32" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="R32" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
+        <v>214</v>
+      </c>
+      <c r="T32" s="32"/>
+      <c r="W32" s="13" t="s">
+        <v>291</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA32" s="26" t="s">
+        <v>287</v>
+      </c>
+      <c r="AB32" s="33" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="33" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -3045,7 +3253,7 @@
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -3054,18 +3262,30 @@
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
       <c r="O33" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="P33" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="R33" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
+        <v>215</v>
+      </c>
+      <c r="T33" s="32"/>
+      <c r="W33" t="s">
+        <v>292</v>
+      </c>
+      <c r="X33" s="36" t="s">
+        <v>287</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>281</v>
+      </c>
+      <c r="AA33" s="26"/>
+      <c r="AB33" s="33"/>
+    </row>
+    <row r="34" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -3073,7 +3293,7 @@
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -3081,10 +3301,26 @@
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="O34" t="s">
+        <v>54</v>
+      </c>
+      <c r="P34" t="s">
+        <v>216</v>
+      </c>
+      <c r="R34" t="s">
+        <v>216</v>
+      </c>
+      <c r="T34" s="32"/>
+      <c r="W34" t="s">
+        <v>289</v>
+      </c>
+      <c r="X34" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="35" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -3092,7 +3328,7 @@
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -3100,913 +3336,1241 @@
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A36" s="3" t="s">
-        <v>77</v>
-      </c>
+      <c r="R35" t="s">
+        <v>220</v>
+      </c>
+      <c r="T35" s="32"/>
+      <c r="W35" t="s">
+        <v>290</v>
+      </c>
+      <c r="X35" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="36" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A36" s="3"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
-      <c r="G36" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>159</v>
-      </c>
+      <c r="G36" s="3"/>
+      <c r="H36" s="1"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
-      <c r="O36" t="s">
-        <v>60</v>
-      </c>
-      <c r="P36" s="19" t="s">
-        <v>217</v>
-      </c>
-      <c r="R36" s="19" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A37" s="3" t="s">
-        <v>78</v>
-      </c>
+      <c r="R36" t="s">
+        <v>273</v>
+      </c>
+      <c r="T36" s="32"/>
+      <c r="W36" t="s">
+        <v>223</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>288</v>
+      </c>
+      <c r="AA36" s="26" t="s">
+        <v>287</v>
+      </c>
+      <c r="AB36" s="33" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="37" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A37" s="3"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
-      <c r="G37" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>159</v>
-      </c>
+      <c r="G37" s="3"/>
+      <c r="H37" s="1"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
-      <c r="O37" t="s">
-        <v>61</v>
-      </c>
-      <c r="P37" s="18" t="s">
-        <v>218</v>
-      </c>
-      <c r="R37" s="18" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A38" s="3" t="s">
-        <v>79</v>
-      </c>
+      <c r="R37" t="s">
+        <v>222</v>
+      </c>
+      <c r="T37" s="32"/>
+      <c r="Z37" t="s">
+        <v>281</v>
+      </c>
+      <c r="AA37" s="26"/>
+      <c r="AB37" s="33"/>
+    </row>
+    <row r="38" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A38" s="3"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
-      <c r="G38" s="3" t="s">
-        <v>77</v>
-      </c>
+      <c r="G38" s="3"/>
+      <c r="H38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
-      <c r="O38" t="s">
-        <v>62</v>
-      </c>
-      <c r="P38" t="s">
-        <v>219</v>
-      </c>
-      <c r="R38" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A39" s="3" t="s">
-        <v>81</v>
-      </c>
+      <c r="R38" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="S38" t="s">
+        <v>147</v>
+      </c>
+      <c r="T38" s="32"/>
+    </row>
+    <row r="39" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A39" s="3"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
-      <c r="G39" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="H39" t="s">
-        <v>160</v>
-      </c>
+      <c r="G39" s="3"/>
+      <c r="H39" s="1"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A40" s="3" t="s">
-        <v>65</v>
-      </c>
+      <c r="R39" t="s">
+        <v>259</v>
+      </c>
+      <c r="T39" s="32"/>
+    </row>
+    <row r="40" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A40" s="3"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
-      <c r="G40" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>153</v>
-      </c>
+      <c r="G40" s="3"/>
+      <c r="H40" s="1"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
-      <c r="O40" t="s">
-        <v>77</v>
-      </c>
-      <c r="P40" t="s">
-        <v>220</v>
-      </c>
       <c r="R40" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A41" s="3" t="s">
-        <v>67</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="T40" s="32"/>
+      <c r="Z40" t="s">
+        <v>279</v>
+      </c>
+      <c r="AA40" s="36" t="s">
+        <v>287</v>
+      </c>
+      <c r="AB40" s="33" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="41" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A41" s="3"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
-      <c r="G41" s="3" t="s">
-        <v>61</v>
-      </c>
+      <c r="G41" s="3"/>
+      <c r="H41" s="1"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
-      <c r="O41" t="s">
-        <v>78</v>
-      </c>
-      <c r="P41" t="s">
-        <v>221</v>
-      </c>
       <c r="R41" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A42" s="3" t="s">
-        <v>68</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="T41" s="32"/>
+      <c r="Z41" t="s">
+        <v>258</v>
+      </c>
+      <c r="AA41" s="36"/>
+      <c r="AB41" s="33"/>
+    </row>
+    <row r="42" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A42" s="3"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
-      <c r="G42" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>153</v>
-      </c>
+      <c r="G42" s="3"/>
+      <c r="H42" s="1"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
-      <c r="O42" t="s">
-        <v>79</v>
-      </c>
-      <c r="P42" t="s">
-        <v>222</v>
-      </c>
       <c r="R42" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A43" s="3" t="s">
-        <v>69</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="T42" s="32"/>
+    </row>
+    <row r="43" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A43" s="3"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
-      <c r="G43" s="3" t="s">
-        <v>152</v>
-      </c>
+      <c r="G43" s="3"/>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
-      <c r="O43" t="s">
-        <v>81</v>
-      </c>
-      <c r="P43" t="s">
-        <v>223</v>
-      </c>
       <c r="R43" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A44" s="3" t="s">
-        <v>70</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="T43" s="32"/>
+    </row>
+    <row r="44" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A44" s="3"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
-      <c r="G44" s="1" t="s">
-        <v>90</v>
-      </c>
+      <c r="G44" s="3"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
       <c r="M44" s="1"/>
-    </row>
-    <row r="45" spans="1:18" ht="34" x14ac:dyDescent="0.2">
-      <c r="A45" s="3" t="s">
-        <v>106</v>
-      </c>
+      <c r="T44" s="32"/>
+    </row>
+    <row r="45" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A45" s="3"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
-      <c r="G45" s="3" t="s">
-        <v>92</v>
-      </c>
+      <c r="G45" s="3"/>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
       <c r="M45" s="1"/>
-      <c r="N45" s="17" t="s">
-        <v>224</v>
-      </c>
-      <c r="O45" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A46" s="3" t="s">
-        <v>107</v>
-      </c>
+      <c r="T45" s="32"/>
+    </row>
+    <row r="46" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A46" s="3"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
-      <c r="G46" s="3" t="s">
-        <v>84</v>
-      </c>
+      <c r="G46" s="3"/>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
       <c r="M46" s="1"/>
-      <c r="O46" t="s">
-        <v>148</v>
-      </c>
-      <c r="P46" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A47" s="3" t="s">
-        <v>84</v>
-      </c>
+    </row>
+    <row r="47" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A47" s="3"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
-      <c r="G47" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>170</v>
-      </c>
+      <c r="G47" s="3"/>
+      <c r="H47" s="1"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
       <c r="M47" s="1"/>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
+      <c r="G48" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H48" s="1"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
       <c r="M48" s="1"/>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="R48" t="s">
+        <v>282</v>
+      </c>
+      <c r="S48" s="26" t="s">
+        <v>287</v>
+      </c>
+      <c r="T48" s="33" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
-      <c r="H49" s="1"/>
+      <c r="G49" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>159</v>
+      </c>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
       <c r="M49" s="1"/>
       <c r="O49" t="s">
-        <v>84</v>
-      </c>
-      <c r="P49" t="s">
-        <v>84</v>
-      </c>
-      <c r="R49" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
+        <v>60</v>
+      </c>
+      <c r="P49" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="R49" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="S49" s="26"/>
+      <c r="T49" s="33"/>
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="I50" s="1"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
       <c r="M50" s="1"/>
       <c r="O50" t="s">
-        <v>152</v>
-      </c>
-      <c r="P50" t="s">
-        <v>86</v>
+        <v>61</v>
+      </c>
+      <c r="P50" s="18" t="s">
+        <v>218</v>
       </c>
       <c r="R50" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.2">
+        <v>264</v>
+      </c>
+      <c r="S50" t="s">
+        <v>147</v>
+      </c>
+      <c r="T50" s="33"/>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
       <c r="M51" s="1"/>
       <c r="O51" t="s">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="P51" t="s">
-        <v>88</v>
+        <v>219</v>
       </c>
       <c r="R51" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.2">
+        <v>267</v>
+      </c>
+      <c r="T51" s="33"/>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="H52" t="s">
+        <v>160</v>
+      </c>
+      <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
       <c r="M52" s="1"/>
-      <c r="O52" t="s">
-        <v>90</v>
-      </c>
-      <c r="P52" t="s">
-        <v>90</v>
-      </c>
-      <c r="R52" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
-        <v>112</v>
+        <v>65</v>
       </c>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I53" s="1"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
       <c r="M53" s="1"/>
       <c r="O53" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="P53" t="s">
-        <v>227</v>
-      </c>
-      <c r="R53" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.2">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
-        <v>126</v>
+        <v>67</v>
       </c>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I54" s="1"/>
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
       <c r="L54" s="1"/>
       <c r="M54" s="1"/>
-      <c r="O54" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="P54" s="20" t="s">
-        <v>243</v>
+      <c r="O54" t="s">
+        <v>78</v>
+      </c>
+      <c r="P54" t="s">
+        <v>221</v>
       </c>
       <c r="R54" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.2">
+        <v>280</v>
+      </c>
+      <c r="S54" t="s">
+        <v>287</v>
+      </c>
+      <c r="T54" s="30" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A55" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I55" s="1"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
       <c r="L55" s="1"/>
       <c r="M55" s="1"/>
-      <c r="O55" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="P55" s="20" t="s">
-        <v>243</v>
+      <c r="O55" t="s">
+        <v>79</v>
+      </c>
+      <c r="P55" t="s">
+        <v>222</v>
       </c>
       <c r="R55" t="s">
-        <v>265</v>
-      </c>
-      <c r="S55" s="19"/>
-    </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.2">
+        <v>281</v>
+      </c>
+      <c r="T55" s="30"/>
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A56" s="3" t="s">
+        <v>69</v>
+      </c>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
       <c r="L56" s="1"/>
       <c r="M56" s="1"/>
-      <c r="O56" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="P56" s="20" t="s">
-        <v>243</v>
-      </c>
-      <c r="R56" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A57" s="1"/>
+      <c r="O56" t="s">
+        <v>81</v>
+      </c>
+      <c r="P56" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A57" s="3" t="s">
+        <v>70</v>
+      </c>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
-      <c r="F57" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="G57" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="H57" s="5"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H57" s="1"/>
       <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
       <c r="K57" s="1"/>
       <c r="L57" s="1"/>
       <c r="M57" s="1"/>
-      <c r="O57" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="P57" s="20" t="s">
-        <v>243</v>
-      </c>
-      <c r="R57" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A58" s="1"/>
+    </row>
+    <row r="58" spans="1:20" ht="34" x14ac:dyDescent="0.2">
+      <c r="A58" s="3" t="s">
+        <v>106</v>
+      </c>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
-      <c r="G58" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="H58" s="5" t="s">
-        <v>163</v>
-      </c>
+      <c r="G58" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H58" s="1"/>
       <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
       <c r="M58" s="1"/>
-      <c r="O58" s="1"/>
-      <c r="P58" s="20"/>
-    </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A59" s="1"/>
+      <c r="N58" s="17" t="s">
+        <v>224</v>
+      </c>
+      <c r="O58" t="s">
+        <v>140</v>
+      </c>
+      <c r="R58" t="s">
+        <v>145</v>
+      </c>
+      <c r="S58" t="s">
+        <v>287</v>
+      </c>
+      <c r="T58" s="32" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A59" s="3" t="s">
+        <v>107</v>
+      </c>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
-      <c r="G59" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="H59" s="5"/>
+      <c r="G59" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="H59" s="1"/>
       <c r="I59" s="1"/>
-      <c r="J59" s="3"/>
+      <c r="J59" s="1"/>
       <c r="K59" s="1"/>
       <c r="L59" s="1"/>
       <c r="M59" s="1"/>
-    </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A60" s="1"/>
+      <c r="O59" t="s">
+        <v>148</v>
+      </c>
+      <c r="P59" t="s">
+        <v>226</v>
+      </c>
+      <c r="R59" t="s">
+        <v>146</v>
+      </c>
+      <c r="T59" s="32"/>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A60" s="3" t="s">
+        <v>84</v>
+      </c>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
-      <c r="G60" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="H60" s="5"/>
+      <c r="G60" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>170</v>
+      </c>
       <c r="I60" s="1"/>
+      <c r="J60" s="1"/>
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
       <c r="M60" s="1"/>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A61" s="7" t="s">
-        <v>154</v>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A61" s="3" t="s">
+        <v>86</v>
       </c>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
-      <c r="G61" s="1"/>
-      <c r="H61" s="1"/>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
       <c r="K61" s="1"/>
       <c r="L61" s="1"/>
       <c r="M61" s="1"/>
-    </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
-        <v>155</v>
-      </c>
+      <c r="R61" t="s">
+        <v>294</v>
+      </c>
+      <c r="S61" s="26" t="s">
+        <v>287</v>
+      </c>
+      <c r="T61" s="32" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A62" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B62" s="1"/>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
       <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
-    </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
+      <c r="J62" s="1"/>
+      <c r="K62" s="1"/>
+      <c r="L62" s="1"/>
+      <c r="M62" s="1"/>
+      <c r="O62" t="s">
+        <v>84</v>
+      </c>
+      <c r="P62" t="s">
+        <v>84</v>
+      </c>
+      <c r="R62" t="s">
+        <v>282</v>
+      </c>
+      <c r="S62" s="26"/>
+      <c r="T62" s="32"/>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A63" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B63" s="1"/>
+      <c r="C63" s="1"/>
+      <c r="D63" s="1"/>
+      <c r="E63" s="1"/>
+      <c r="J63" s="1"/>
+      <c r="K63" s="1"/>
+      <c r="L63" s="1"/>
+      <c r="M63" s="1"/>
+      <c r="O63" t="s">
+        <v>152</v>
+      </c>
+      <c r="P63" t="s">
+        <v>86</v>
+      </c>
+      <c r="R63" t="s">
+        <v>284</v>
+      </c>
+      <c r="T63" s="32"/>
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A64" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B64" s="1"/>
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
+      <c r="E64" s="1"/>
+      <c r="J64" s="1"/>
+      <c r="K64" s="1"/>
+      <c r="L64" s="1"/>
+      <c r="M64" s="1"/>
+      <c r="O64" t="s">
+        <v>88</v>
+      </c>
+      <c r="P64" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A65" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B65" s="1"/>
+      <c r="C65" s="1"/>
+      <c r="D65" s="1"/>
+      <c r="E65" s="1"/>
+      <c r="J65" s="1"/>
+      <c r="K65" s="1"/>
+      <c r="L65" s="1"/>
+      <c r="M65" s="1"/>
+      <c r="O65" t="s">
+        <v>90</v>
+      </c>
+      <c r="P65" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A66" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B66" s="1"/>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="J66" s="1"/>
+      <c r="K66" s="1"/>
+      <c r="L66" s="1"/>
+      <c r="M66" s="1"/>
+      <c r="O66" t="s">
+        <v>92</v>
+      </c>
+      <c r="P66" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A67" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B67" s="1"/>
+      <c r="C67" s="1"/>
+      <c r="D67" s="1"/>
+      <c r="E67" s="1"/>
+      <c r="J67" s="1"/>
+      <c r="K67" s="1"/>
+      <c r="L67" s="1"/>
+      <c r="M67" s="1"/>
+      <c r="O67" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="P67" s="20" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="B68" s="1"/>
+      <c r="C68" s="1"/>
+      <c r="D68" s="1"/>
+      <c r="E68" s="1"/>
+      <c r="J68" s="1"/>
+      <c r="K68" s="1"/>
+      <c r="L68" s="1"/>
+      <c r="M68" s="1"/>
+      <c r="O68" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="P68" s="20" t="s">
+        <v>243</v>
+      </c>
+      <c r="S68" s="19"/>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="B69" s="1"/>
+      <c r="C69" s="1"/>
+      <c r="D69" s="1"/>
+      <c r="E69" s="1"/>
+      <c r="J69" s="1"/>
+      <c r="K69" s="1"/>
+      <c r="L69" s="1"/>
+      <c r="M69" s="1"/>
+      <c r="O69" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="P69" s="20" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A70" s="1"/>
+      <c r="B70" s="1"/>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="G70" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="H70" s="5"/>
+      <c r="I70" s="1"/>
+      <c r="K70" s="1"/>
+      <c r="L70" s="1"/>
+      <c r="M70" s="1"/>
+      <c r="O70" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="P70" s="20" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A71" s="1"/>
+      <c r="B71" s="1"/>
+      <c r="C71" s="1"/>
+      <c r="D71" s="1"/>
+      <c r="E71" s="1"/>
+      <c r="F71" s="1"/>
+      <c r="G71" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="H71" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="I71" s="1"/>
+      <c r="K71" s="1"/>
+      <c r="L71" s="1"/>
+      <c r="M71" s="1"/>
+      <c r="O71" s="1"/>
+      <c r="P71" s="20"/>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A72" s="1"/>
+      <c r="B72" s="1"/>
+      <c r="C72" s="1"/>
+      <c r="D72" s="1"/>
+      <c r="E72" s="1"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="H72" s="5"/>
+      <c r="I72" s="1"/>
+      <c r="J72" s="3"/>
+      <c r="K72" s="1"/>
+      <c r="L72" s="1"/>
+      <c r="M72" s="1"/>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A73" s="1"/>
+      <c r="B73" s="1"/>
+      <c r="C73" s="1"/>
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="H73" s="5"/>
+      <c r="I73" s="1"/>
+      <c r="K73" s="1"/>
+      <c r="L73" s="1"/>
+      <c r="M73" s="1"/>
+    </row>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A74" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="B74" s="1"/>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="1"/>
+      <c r="K74" s="1"/>
+      <c r="L74" s="1"/>
+      <c r="M74" s="1"/>
+    </row>
+    <row r="75" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>155</v>
+      </c>
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
+    </row>
+    <row r="76" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
         <v>156</v>
       </c>
-      <c r="F63" s="1"/>
-      <c r="G63" s="4" t="s">
+      <c r="F76" s="1"/>
+      <c r="G76" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="H63" s="1" t="s">
+      <c r="H76" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="I63" s="1"/>
-    </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
+      <c r="I76" s="1"/>
+    </row>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
         <v>157</v>
       </c>
-      <c r="F64" s="1"/>
-      <c r="G64" s="7" t="s">
+      <c r="F77" s="1"/>
+      <c r="G77" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="H64" s="1"/>
-      <c r="I64" s="1"/>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+    </row>
+    <row r="78" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
         <v>172</v>
       </c>
-      <c r="F65" s="1"/>
-      <c r="G65" s="7" t="s">
+      <c r="F78" s="1"/>
+      <c r="G78" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="F66" s="1"/>
-      <c r="G66" s="1" t="s">
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+    </row>
+    <row r="79" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="F79" s="1"/>
+      <c r="G79" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H66" s="1"/>
-      <c r="I66" s="1"/>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
+      <c r="H79" s="1"/>
+      <c r="I79" s="1"/>
+    </row>
+    <row r="80" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
         <v>161</v>
       </c>
-      <c r="F67" s="1"/>
-      <c r="G67" s="1" t="s">
+      <c r="F80" s="1"/>
+      <c r="G80" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="H67" s="1"/>
-      <c r="I67" s="1"/>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="F68" s="1"/>
-      <c r="G68" s="1" t="s">
+      <c r="H80" s="1"/>
+      <c r="I80" s="1"/>
+    </row>
+    <row r="81" spans="6:17" x14ac:dyDescent="0.2">
+      <c r="F81" s="1"/>
+      <c r="G81" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="H68" s="1"/>
-      <c r="I68" s="1"/>
-    </row>
-    <row r="69" spans="1:16" ht="46" x14ac:dyDescent="0.2">
-      <c r="G69" s="1" t="s">
+      <c r="H81" s="1"/>
+      <c r="I81" s="1"/>
+    </row>
+    <row r="82" spans="6:17" ht="46" x14ac:dyDescent="0.2">
+      <c r="G82" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="H69" s="1"/>
-      <c r="O69" s="21" t="s">
+      <c r="H82" s="1"/>
+      <c r="O82" s="21" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="70" spans="1:16" ht="17" x14ac:dyDescent="0.2">
-      <c r="G70" s="1" t="s">
+    <row r="83" spans="6:17" ht="17" x14ac:dyDescent="0.2">
+      <c r="G83" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="N70" s="17" t="s">
+      <c r="N83" s="17" t="s">
         <v>228</v>
       </c>
-      <c r="O70" t="s">
+      <c r="O83" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="N71" t="s">
+      <c r="Q83" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="84" spans="6:17" x14ac:dyDescent="0.2">
+      <c r="N84" t="s">
         <v>229</v>
       </c>
-      <c r="O71" t="s">
+      <c r="O84" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="G72" s="4" t="s">
+      <c r="Q84" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="85" spans="6:17" x14ac:dyDescent="0.2">
+      <c r="G85" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="H72" s="1" t="s">
+      <c r="H85" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="N72" t="s">
+      <c r="N85" t="s">
         <v>230</v>
       </c>
-      <c r="O72" s="1" t="s">
+      <c r="O85" s="1" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="G73" s="7" t="s">
+      <c r="Q85" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="86" spans="6:17" x14ac:dyDescent="0.2">
+      <c r="G86" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="N73" t="s">
+      <c r="N86" t="s">
         <v>231</v>
       </c>
-      <c r="O73" s="1" t="s">
+      <c r="O86" s="1" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="G74" s="1" t="s">
+      <c r="Q86" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="87" spans="6:17" x14ac:dyDescent="0.2">
+      <c r="G87" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="O74" s="1"/>
-    </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="G75" s="1" t="s">
+      <c r="O87" s="1"/>
+    </row>
+    <row r="88" spans="6:17" x14ac:dyDescent="0.2">
+      <c r="G88" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="76" spans="1:16" ht="51" x14ac:dyDescent="0.2">
-      <c r="G76" s="1" t="s">
+    <row r="89" spans="6:17" ht="51" x14ac:dyDescent="0.2">
+      <c r="G89" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="P76" s="22" t="s">
+      <c r="P89" s="22" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="G77" s="1" t="s">
+    <row r="90" spans="6:17" x14ac:dyDescent="0.2">
+      <c r="G90" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="P77" t="s">
+      <c r="P90" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="P78" s="19" t="s">
+    <row r="91" spans="6:17" x14ac:dyDescent="0.2">
+      <c r="P91" s="19" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="G79" s="4" t="s">
+    <row r="92" spans="6:17" x14ac:dyDescent="0.2">
+      <c r="G92" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="H79" s="1"/>
-      <c r="P79" t="s">
+      <c r="H92" s="1"/>
+      <c r="P92" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="G80" s="7" t="s">
+    <row r="93" spans="6:17" x14ac:dyDescent="0.2">
+      <c r="G93" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="P80" s="19" t="s">
+      <c r="P93" s="19" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="81" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G81" s="1" t="s">
+    <row r="94" spans="6:17" x14ac:dyDescent="0.2">
+      <c r="G94" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="P81" t="s">
+      <c r="P94" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="82" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G82" s="1"/>
-    </row>
-    <row r="83" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G83" s="4" t="s">
+    <row r="95" spans="6:17" x14ac:dyDescent="0.2">
+      <c r="G95" s="1"/>
+    </row>
+    <row r="96" spans="6:17" x14ac:dyDescent="0.2">
+      <c r="G96" s="4" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="84" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G84" s="7" t="s">
+    <row r="97" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="G97" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="N84" s="13" t="s">
+      <c r="N97" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="O84" s="13">
+      <c r="O97" s="13">
         <v>50</v>
       </c>
-      <c r="P84" s="13">
+      <c r="P97" s="13">
         <v>53</v>
       </c>
     </row>
-    <row r="85" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G85" s="1" t="s">
+    <row r="98" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="G98" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="N85" t="s">
+      <c r="N98" t="s">
         <v>236</v>
       </c>
-      <c r="O85" t="s">
+      <c r="O98" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="86" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G86" s="1"/>
-      <c r="O86" t="s">
+    <row r="99" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="G99" s="1"/>
+      <c r="O99" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="87" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G87" s="4" t="s">
+    <row r="100" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="G100" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="H87" s="1" t="s">
+      <c r="H100" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="O87" t="s">
+      <c r="O100" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="88" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G88" s="7" t="s">
+    <row r="101" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="G101" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="O88" t="s">
+      <c r="O101" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="89" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G89" s="7" t="s">
+    <row r="102" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="G102" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="H89" s="1"/>
-      <c r="O89" t="s">
+      <c r="H102" s="1"/>
+      <c r="O102" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="90" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G90" s="1" t="s">
+    <row r="103" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="G103" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="O90" t="s">
+      <c r="O103" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="91" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="O91" t="s">
+    <row r="104" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="O104" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="92" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G92" s="4" t="s">
+    <row r="105" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="G105" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="O92" t="s">
+      <c r="O105" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="93" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G93" s="7" t="s">
+    <row r="106" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="G106" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="O93" t="s">
+      <c r="O106" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="94" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G94" s="1" t="s">
+    <row r="107" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="G107" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="95" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="N95" t="s">
+    <row r="108" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="N108" t="s">
         <v>237</v>
       </c>
-      <c r="O95" t="s">
+      <c r="O108" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="96" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="O96" t="s">
+    <row r="109" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="O109" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="98" spans="7:15" x14ac:dyDescent="0.2">
-      <c r="N98" s="13" t="s">
+    <row r="111" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="N111" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="O98" s="13">
+      <c r="O111" s="13">
         <v>11</v>
       </c>
     </row>
-    <row r="101" spans="7:15" x14ac:dyDescent="0.2">
-      <c r="G101" s="13"/>
+    <row r="114" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G114" s="13"/>
     </row>
   </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="S61:S62"/>
+    <mergeCell ref="T61:T63"/>
+    <mergeCell ref="AA32:AA33"/>
+    <mergeCell ref="AB32:AB33"/>
+    <mergeCell ref="AA36:AA37"/>
+    <mergeCell ref="AB36:AB37"/>
+    <mergeCell ref="AB40:AB41"/>
+    <mergeCell ref="AB20:AB28"/>
+    <mergeCell ref="T20:T45"/>
+    <mergeCell ref="S48:S49"/>
+    <mergeCell ref="T48:T51"/>
+    <mergeCell ref="T54:T55"/>
+    <mergeCell ref="T58:T59"/>
+    <mergeCell ref="T2:T6"/>
+    <mergeCell ref="T14:T17"/>
+    <mergeCell ref="T9:T10"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4375,7 +4939,7 @@
       <c r="A49" t="s">
         <v>265</v>
       </c>
-      <c r="B49" s="25" t="s">
+      <c r="B49" s="24" t="s">
         <v>277</v>
       </c>
     </row>
@@ -4383,7 +4947,7 @@
       <c r="A50" t="s">
         <v>266</v>
       </c>
-      <c r="B50" s="25" t="s">
+      <c r="B50" s="24" t="s">
         <v>277</v>
       </c>
     </row>
